--- a/Data/Results/Master_Summary/Training_Data/EV_ICE_Training_NONSTRICT.xlsx
+++ b/Data/Results/Master_Summary/Training_Data/EV_ICE_Training_NONSTRICT.xlsx
@@ -11,7 +11,7 @@
     <sheet name="02_Feature_Groups" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_Training_Data'!$A$4:$BI$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_Training_Data'!$A$4:$BI$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI32"/>
+  <dimension ref="A1:BI44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -970,27 +970,27 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>30-07-2026</t>
+          <t>29-07-2026</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>12:00:06</t>
+          <t>08:36:08</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>13:38:16</t>
+          <t>14:19:59</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>01:54:40</t>
+          <t>22:58:13</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>03:20:13</t>
+          <t>04:09:43</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -999,151 +999,151 @@
         </is>
       </c>
       <c r="M5" s="5" t="n">
-        <v>605.4333333333334</v>
+        <v>577.9166666666666</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>102.5403079815431</v>
+        <v>305.1665869122799</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>98.16888333333333</v>
+        <v>343.8404</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>76.08025778994646</v>
+        <v>69.11154120244322</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>102.5404226319246</v>
+        <v>310.4742418277487</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>85.5448</v>
+        <v>311.5075166666667</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>76.61984720324178</v>
+        <v>63.46076786637193</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>0</v>
+        <v>0.3133132329092165</v>
       </c>
       <c r="W5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>0</v>
+        <v>0.626626465818433</v>
       </c>
       <c r="Y5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>10.5</v>
+        <v>23.65</v>
       </c>
       <c r="AA5" s="5" t="n">
-        <v>5.333333333333333</v>
+        <v>18.1</v>
       </c>
       <c r="AB5" s="5" t="n">
-        <v>0.02708574234946004</v>
+        <v>0.04165231879405064</v>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>0.1105839661259325</v>
+        <v>0.2136487015115684</v>
       </c>
       <c r="AD5" s="5" t="n">
-        <v>0.1547756705683431</v>
+        <v>0.1056718447206359</v>
       </c>
       <c r="AE5" s="5" t="n">
-        <v>1.244069618916741</v>
+        <v>0.7082277398173538</v>
       </c>
       <c r="AF5" s="5" t="n">
-        <v>6.85</v>
+        <v>25.7</v>
       </c>
       <c r="AG5" s="5" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>0.03453093426685515</v>
+        <v>0.155968406398383</v>
       </c>
       <c r="AI5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>0.3024607381038407</v>
+        <v>0.3641285752491432</v>
       </c>
       <c r="AK5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" s="5" t="n">
-        <v>1.466666666666667</v>
+        <v>7.6</v>
       </c>
       <c r="AM5" s="5" t="n">
-        <v>0.9166666666666666</v>
+        <v>1.75</v>
       </c>
       <c r="AN5" s="5" t="n">
-        <v>0.08000017609170872</v>
+        <v>0.4492738025976991</v>
       </c>
       <c r="AO5" s="5" t="n">
-        <v>0.1014311759756502</v>
+        <v>0.3073128194596925</v>
       </c>
       <c r="AP5" s="5" t="n">
-        <v>3.272734476478992</v>
+        <v>3.546898441560783</v>
       </c>
       <c r="AQ5" s="5" t="n">
-        <v>6.639131518406194</v>
+        <v>10.53643952433232</v>
       </c>
       <c r="AR5" s="5" t="n">
-        <v>15.36666666666667</v>
+        <v>61.42373333333333</v>
       </c>
       <c r="AS5" s="5" t="n">
-        <v>10.36666666666667</v>
+        <v>57.69085</v>
       </c>
       <c r="AT5" s="5" t="n">
-        <v>15.89297941842838</v>
+        <v>60.30869650602873</v>
       </c>
       <c r="AU5" s="5" t="n">
-        <v>12.28082445094132</v>
+        <v>55.580881691352</v>
       </c>
       <c r="AV5" s="5" t="n">
-        <v>62.055017251998</v>
+        <v>58.91080847731589</v>
       </c>
       <c r="AW5" s="5" t="n">
-        <v>71.07872672570537</v>
+        <v>57.80557751326458</v>
       </c>
       <c r="AX5" s="5" t="n">
-        <v>9.133333333333333</v>
+        <v>45.18333333333333</v>
       </c>
       <c r="AY5" s="5" t="n">
-        <v>6.283333333333333</v>
+        <v>41.38333333333333</v>
       </c>
       <c r="AZ5" s="5" t="n">
-        <v>9.410558976194402</v>
+        <v>44.61908932592698</v>
       </c>
       <c r="BA5" s="5" t="n">
-        <v>7.766673171881417</v>
+        <v>38.88632527176938</v>
       </c>
       <c r="BB5" s="5" t="n">
-        <v>61.82119035456177</v>
+        <v>59.25072724947884</v>
       </c>
       <c r="BC5" s="5" t="n">
-        <v>74.16451835218329</v>
+        <v>56.37969028528786</v>
       </c>
       <c r="BD5" s="5" t="n">
-        <v>54.85221666666666</v>
+        <v>150.2833333333333</v>
       </c>
       <c r="BE5" s="5" t="n">
-        <v>62.6448</v>
+        <v>192.5166666666667</v>
       </c>
       <c r="BF5" s="5" t="n">
-        <v>77.09515273421231</v>
+        <v>199.2785933196247</v>
       </c>
       <c r="BG5" s="5" t="n">
-        <v>82.2809098670003</v>
+        <v>215.4860733436561</v>
       </c>
       <c r="BH5" s="5" t="n">
-        <v>84.33039620190503</v>
+        <v>79.56115514590762</v>
       </c>
       <c r="BI5" s="5" t="n">
-        <v>78.80709319879732</v>
+        <v>67.15867578886345</v>
       </c>
     </row>
     <row r="6">
@@ -1177,27 +1177,27 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>06-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>12:30:40</t>
+          <t>08:36:08</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>12:55:57</t>
+          <t>14:19:59</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>02:39:21</t>
+          <t>23:15:55</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>02:59:42</t>
+          <t>04:14:56</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -1206,151 +1206,151 @@
         </is>
       </c>
       <c r="M6" s="7" t="n">
-        <v>591.3166666666666</v>
+        <v>560.2166666666666</v>
       </c>
       <c r="N6" s="7" t="n">
-        <v>27.18076401749682</v>
+        <v>305.1072776594863</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>25.27086666666667</v>
+        <v>343.8404</v>
       </c>
       <c r="P6" s="7" t="n">
-        <v>72.17266749628908</v>
+        <v>69.09808681934425</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>27.2938636578444</v>
+        <v>305.2160753980956</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>20.34321666666666</v>
+        <v>299.0182166666667</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>80.50014146258407</v>
+        <v>66.42225595059593</v>
       </c>
       <c r="T6" s="7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="U6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="7" t="n">
-        <v>0</v>
+        <v>0.3133132329092165</v>
       </c>
       <c r="W6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="X6" s="7" t="n">
-        <v>0</v>
+        <v>0.626626465818433</v>
       </c>
       <c r="Y6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z6" s="7" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="AA6" s="7" t="n">
-        <v>0</v>
+        <v>16.43333333333333</v>
       </c>
       <c r="AB6" s="7" t="n">
-        <v>0</v>
+        <v>0.04165231879405064</v>
       </c>
       <c r="AC6" s="7" t="n">
-        <v>0</v>
+        <v>0.08388219724002884</v>
       </c>
       <c r="AD6" s="7" t="n">
-        <v>0</v>
+        <v>0.1056718447206359</v>
       </c>
       <c r="AE6" s="7" t="n">
-        <v>0</v>
+        <v>0.3062636004706936</v>
       </c>
       <c r="AF6" s="7" t="n">
-        <v>2.683333333333333</v>
+        <v>25.7</v>
       </c>
       <c r="AG6" s="7" t="n">
-        <v>0</v>
+        <v>6.983333333333333</v>
       </c>
       <c r="AH6" s="7" t="n">
-        <v>0.01072180369660728</v>
+        <v>0.155968406398383</v>
       </c>
       <c r="AI6" s="7" t="n">
-        <v>0</v>
+        <v>0.03091495950618035</v>
       </c>
       <c r="AJ6" s="7" t="n">
-        <v>0.2397421944582994</v>
+        <v>0.3641285752491432</v>
       </c>
       <c r="AK6" s="7" t="n">
-        <v>0</v>
+        <v>0.2656177905065615</v>
       </c>
       <c r="AL6" s="7" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AM6" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN6" s="7" t="n">
-        <v>0</v>
+        <v>0.4492738025976991</v>
       </c>
       <c r="AO6" s="7" t="n">
-        <v>0</v>
+        <v>0.2309310830082773</v>
       </c>
       <c r="AP6" s="7" t="n">
-        <v>0</v>
+        <v>3.546898441560783</v>
       </c>
       <c r="AQ6" s="7" t="n">
-        <v>0</v>
+        <v>2.771172996099328</v>
       </c>
       <c r="AR6" s="7" t="n">
-        <v>6.766666666666667</v>
+        <v>61.42373333333333</v>
       </c>
       <c r="AS6" s="7" t="n">
-        <v>3.466666666666667</v>
+        <v>60.01821666666667</v>
       </c>
       <c r="AT6" s="7" t="n">
-        <v>6.807982530871882</v>
+        <v>60.30149638549678</v>
       </c>
       <c r="AU6" s="7" t="n">
-        <v>4.402529837201792</v>
+        <v>57.92889382509147</v>
       </c>
       <c r="AV6" s="7" t="n">
-        <v>60.36634756438122</v>
+        <v>58.90377524751248</v>
       </c>
       <c r="AW6" s="7" t="n">
-        <v>76.19763179772332</v>
+        <v>57.91131130751949</v>
       </c>
       <c r="AX6" s="7" t="n">
-        <v>4.183333333333334</v>
+        <v>45.18333333333333</v>
       </c>
       <c r="AY6" s="7" t="n">
-        <v>3.033333333333333</v>
+        <v>42.63333333333333</v>
       </c>
       <c r="AZ6" s="7" t="n">
-        <v>4.29026687551903</v>
+        <v>44.61908932592698</v>
       </c>
       <c r="BA6" s="7" t="n">
-        <v>3.965547998422918</v>
+        <v>43.16292539518683</v>
       </c>
       <c r="BB6" s="7" t="n">
-        <v>61.53370817477493</v>
+        <v>59.25072724947884</v>
       </c>
       <c r="BC6" s="7" t="n">
-        <v>78.43941095781597</v>
+        <v>60.74532111910579</v>
       </c>
       <c r="BD6" s="7" t="n">
-        <v>11.63753333333333</v>
+        <v>150.2833333333333</v>
       </c>
       <c r="BE6" s="7" t="n">
-        <v>13.84321666666667</v>
+        <v>167.95</v>
       </c>
       <c r="BF6" s="7" t="n">
-        <v>16.0717928074093</v>
+        <v>199.2264841873632</v>
       </c>
       <c r="BG6" s="7" t="n">
-        <v>18.92578582221969</v>
+        <v>203.7785279380628</v>
       </c>
       <c r="BH6" s="7" t="n">
-        <v>82.86185232075739</v>
+        <v>79.54035079011952</v>
       </c>
       <c r="BI6" s="7" t="n">
-        <v>82.02913937390619</v>
+        <v>72.79971227319898</v>
       </c>
     </row>
     <row r="7">
@@ -1384,27 +1384,27 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>31-07-2026</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>04:34:49</t>
+          <t>00:24:16</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>04:53:30</t>
+          <t>06:09:53</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>03:13:12</t>
+          <t>23:25:13</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>03:42:52</t>
+          <t>05:23:37</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1413,67 +1413,67 @@
         </is>
       </c>
       <c r="M7" s="5" t="n">
-        <v>81.61666666666667</v>
+        <v>59.04999999999995</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>11.42391390088974</v>
+        <v>320.3395097107276</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>18.67793333333333</v>
+        <v>345.6166666666667</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>55.44692920604529</v>
+        <v>64.61675662785962</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>11.63657856259103</v>
+        <v>320.689018034049</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>29.6565</v>
+        <v>358.3974333333333</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>59.58783215117909</v>
+        <v>59.67911560660773</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>0</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>0</v>
+        <v>0.3220723959647177</v>
       </c>
       <c r="W7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>0</v>
+        <v>0.5041133154230363</v>
       </c>
       <c r="Y7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>6.55</v>
+        <v>10.56666666666667</v>
       </c>
       <c r="AA7" s="5" t="n">
-        <v>18.05</v>
+        <v>35.98333333333333</v>
       </c>
       <c r="AB7" s="5" t="n">
-        <v>0.2163028850735744</v>
+        <v>0.4696266909337409</v>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>0.1098089982133633</v>
+        <v>0.3473404234144944</v>
       </c>
       <c r="AD7" s="5" t="n">
-        <v>1.981400473956407</v>
+        <v>2.666649980065405</v>
       </c>
       <c r="AE7" s="5" t="n">
-        <v>0.3650160605430359</v>
+        <v>0.5791688394127745</v>
       </c>
       <c r="AF7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AG7" s="5" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AH7" s="5" t="n">
         <v>0</v>
@@ -1488,76 +1488,76 @@
         <v>0</v>
       </c>
       <c r="AL7" s="5" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AM7" s="5" t="n">
-        <v>0</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="AN7" s="5" t="n">
-        <v>0</v>
+        <v>0.2646788011201056</v>
       </c>
       <c r="AO7" s="5" t="n">
-        <v>0</v>
+        <v>0.4374014031543842</v>
       </c>
       <c r="AP7" s="5" t="n">
-        <v>0</v>
+        <v>23.82109210080951</v>
       </c>
       <c r="AQ7" s="5" t="n">
-        <v>0</v>
+        <v>6.427122658595033</v>
       </c>
       <c r="AR7" s="5" t="n">
-        <v>2.5</v>
+        <v>49.31666666666667</v>
       </c>
       <c r="AS7" s="5" t="n">
-        <v>3.2872</v>
+        <v>62.08705</v>
       </c>
       <c r="AT7" s="5" t="n">
-        <v>2.38371396280334</v>
+        <v>46.82863918427439</v>
       </c>
       <c r="AU7" s="5" t="n">
-        <v>3.054887036688835</v>
+        <v>58.41038144450143</v>
       </c>
       <c r="AV7" s="5" t="n">
-        <v>57.20913510728016</v>
+        <v>56.97299799370997</v>
       </c>
       <c r="AW7" s="5" t="n">
-        <v>55.75968064046304</v>
+        <v>56.44692229168702</v>
       </c>
       <c r="AX7" s="5" t="n">
-        <v>3.533333333333333</v>
+        <v>44.58333333333334</v>
       </c>
       <c r="AY7" s="5" t="n">
-        <v>3.433333333333333</v>
+        <v>50.53333333333333</v>
       </c>
       <c r="AZ7" s="5" t="n">
-        <v>1.971912446606221</v>
+        <v>41.95380970861748</v>
       </c>
       <c r="BA7" s="5" t="n">
-        <v>2.822408693852921</v>
+        <v>47.46435945988381</v>
       </c>
       <c r="BB7" s="5" t="n">
-        <v>33.48530569708677</v>
+        <v>56.46120185084968</v>
       </c>
       <c r="BC7" s="5" t="n">
-        <v>49.32364707704134</v>
+        <v>56.35609962255334</v>
       </c>
       <c r="BD7" s="5" t="n">
-        <v>6.0946</v>
+        <v>202.15</v>
       </c>
       <c r="BE7" s="5" t="n">
-        <v>4.885966666666667</v>
+        <v>205.3603833333333</v>
       </c>
       <c r="BF7" s="5" t="n">
-        <v>6.851984606406608</v>
+        <v>230.5006829298171</v>
       </c>
       <c r="BG7" s="5" t="n">
-        <v>5.649473833835908</v>
+        <v>214.0295353030949</v>
       </c>
       <c r="BH7" s="5" t="n">
-        <v>67.45628529918231</v>
+        <v>68.41474635562219</v>
       </c>
       <c r="BI7" s="5" t="n">
-        <v>69.37591947621853</v>
+        <v>62.53286008597583</v>
       </c>
     </row>
     <row r="8">
@@ -2414,32 +2414,32 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
+          <t>15-07-2026</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
           <t>25-09-2026</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>15-07-2026</t>
-        </is>
-      </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>13:45:53</t>
+          <t>08:26:24</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>17:53:09</t>
+          <t>13:25:55</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>11:20:23</t>
+          <t>14:27:10</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>15:54:44</t>
+          <t>19:12:44</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -2448,25 +2448,25 @@
         </is>
       </c>
       <c r="M12" s="7" t="n">
-        <v>145.5</v>
+        <v>360.7666666666667</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>148.4081122812309</v>
+        <v>153.5348441515956</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>247.26765</v>
+        <v>299.5047</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>47.63775321159345</v>
+        <v>41.13690324412203</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>148.1693420519742</v>
+        <v>153.5526617847118</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>274.35</v>
+        <v>285.5666666666667</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>44.79805655414056</v>
+        <v>41.3531214666836</v>
       </c>
       <c r="T12" s="7" t="n">
         <v>0</v>
@@ -2487,121 +2487,121 @@
         <v>0</v>
       </c>
       <c r="Z12" s="7" t="n">
-        <v>35.56666666666667</v>
+        <v>68.95</v>
       </c>
       <c r="AA12" s="7" t="n">
-        <v>69.48333333333333</v>
+        <v>48.18333333333333</v>
       </c>
       <c r="AB12" s="7" t="n">
-        <v>0.5933262321891101</v>
+        <v>0.4749837040150751</v>
       </c>
       <c r="AC12" s="7" t="n">
-        <v>0.8398781436089819</v>
+        <v>0.6526929809004927</v>
       </c>
       <c r="AD12" s="7" t="n">
-        <v>1.000925227685471</v>
+        <v>0.4133288214779479</v>
       </c>
       <c r="AE12" s="7" t="n">
-        <v>0.7252485768751104</v>
+        <v>0.8127619270985035</v>
       </c>
       <c r="AF12" s="7" t="n">
-        <v>26.16571666666666</v>
+        <v>8.15</v>
       </c>
       <c r="AG12" s="7" t="n">
-        <v>9.949999999999999</v>
+        <v>17.66666666666667</v>
       </c>
       <c r="AH12" s="7" t="n">
-        <v>0.5067319571443681</v>
+        <v>0.5758500319474457</v>
       </c>
       <c r="AI12" s="7" t="n">
-        <v>1.797999630400208</v>
+        <v>1.46713538845297</v>
       </c>
       <c r="AJ12" s="7" t="n">
-        <v>1.161975336505673</v>
+        <v>4.239386738263403</v>
       </c>
       <c r="AK12" s="7" t="n">
-        <v>10.84220882653392</v>
+        <v>4.982723960783671</v>
       </c>
       <c r="AL12" s="7" t="n">
-        <v>2.05</v>
+        <v>8.016666666666667</v>
       </c>
       <c r="AM12" s="7" t="n">
-        <v>1.716666666666667</v>
+        <v>9.9</v>
       </c>
       <c r="AN12" s="7" t="n">
-        <v>0.1799078409944621</v>
+        <v>0.6265751975894123</v>
       </c>
       <c r="AO12" s="7" t="n">
-        <v>0.5759078527107181</v>
+        <v>1.3169091629821</v>
       </c>
       <c r="AP12" s="7" t="n">
-        <v>5.265595346179379</v>
+        <v>4.689544098382295</v>
       </c>
       <c r="AQ12" s="7" t="n">
-        <v>20.12881815299597</v>
+        <v>7.981267654436969</v>
       </c>
       <c r="AR12" s="7" t="n">
-        <v>63.03526666666667</v>
+        <v>58.3</v>
       </c>
       <c r="AS12" s="7" t="n">
-        <v>25.13333333333333</v>
+        <v>51.03333333333333</v>
       </c>
       <c r="AT12" s="7" t="n">
-        <v>45.7896379485424</v>
+        <v>45.77282478240121</v>
       </c>
       <c r="AU12" s="7" t="n">
-        <v>16.04368253659841</v>
+        <v>32.19133544608479</v>
       </c>
       <c r="AV12" s="7" t="n">
-        <v>43.58478074568644</v>
+        <v>47.10753836953813</v>
       </c>
       <c r="AW12" s="7" t="n">
-        <v>38.30056838975749</v>
+        <v>37.84742247090309</v>
       </c>
       <c r="AX12" s="7" t="n">
-        <v>45.45</v>
+        <v>42.61666666666667</v>
       </c>
       <c r="AY12" s="7" t="n">
-        <v>23.43333333333333</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="AZ12" s="7" t="n">
-        <v>33.36307095293761</v>
+        <v>32.14941881546432</v>
       </c>
       <c r="BA12" s="7" t="n">
-        <v>16.77959665852362</v>
+        <v>24.26414905968165</v>
       </c>
       <c r="BB12" s="7" t="n">
-        <v>44.04365802368001</v>
+        <v>45.26316297836197</v>
       </c>
       <c r="BC12" s="7" t="n">
-        <v>42.9634053845555</v>
+        <v>39.20598591330966</v>
       </c>
       <c r="BD12" s="7" t="n">
-        <v>75</v>
+        <v>113.4713666666667</v>
       </c>
       <c r="BE12" s="7" t="n">
-        <v>144.6333333333333</v>
+        <v>121.65</v>
       </c>
       <c r="BF12" s="7" t="n">
-        <v>67.97543734942298</v>
+        <v>73.93519162017814</v>
       </c>
       <c r="BG12" s="7" t="n">
-        <v>112.1322772301322</v>
+        <v>93.66043974660975</v>
       </c>
       <c r="BH12" s="7" t="n">
-        <v>54.38034987953838</v>
+        <v>39.09454541287233</v>
       </c>
       <c r="BI12" s="7" t="n">
-        <v>46.51719267440379</v>
+        <v>46.1950380994376</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2616,37 +2616,37 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Pondicherry → Chennai</t>
+          <t>Chennai → Pondicherry</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>16-07-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>18-07-2026</t>
+          <t>15-07-2026</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>14:16:16</t>
+          <t>13:45:53</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>17:07:49</t>
+          <t>17:53:09</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>16:20:34</t>
+          <t>11:20:23</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>19:28:38</t>
+          <t>15:54:44</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -2655,25 +2655,25 @@
         </is>
       </c>
       <c r="M13" s="5" t="n">
-        <v>124.3000000000001</v>
+        <v>145.5</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>126.503272181271</v>
+        <v>148.4081122812309</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>171.54615</v>
+        <v>247.26765</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>51.96681218238075</v>
+        <v>47.63775321159345</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>126.4504264596244</v>
+        <v>148.1693420519742</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>188.0674333333333</v>
+        <v>274.35</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>46.52364975832732</v>
+        <v>44.79805655414056</v>
       </c>
       <c r="T13" s="5" t="n">
         <v>0</v>
@@ -2694,112 +2694,112 @@
         <v>0</v>
       </c>
       <c r="Z13" s="5" t="n">
-        <v>26.36886666666667</v>
+        <v>35.56666666666667</v>
       </c>
       <c r="AA13" s="5" t="n">
-        <v>23.71666666666667</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="AB13" s="5" t="n">
-        <v>0.9969610105345994</v>
+        <v>0.5933262321891101</v>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>0.1169990422600451</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="AD13" s="5" t="n">
-        <v>2.26849569942619</v>
+        <v>1.000925227685471</v>
       </c>
       <c r="AE13" s="5" t="n">
-        <v>0.2959919551202828</v>
+        <v>0.7252485768751104</v>
       </c>
       <c r="AF13" s="5" t="n">
-        <v>0.65</v>
+        <v>26.16571666666666</v>
       </c>
       <c r="AG13" s="5" t="n">
-        <v>2.383333333333333</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AH13" s="5" t="n">
-        <v>0.3292747005187303</v>
+        <v>0.5067319571443681</v>
       </c>
       <c r="AI13" s="5" t="n">
-        <v>0.7448250731105075</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="AJ13" s="5" t="n">
-        <v>30.39458774019049</v>
+        <v>1.161975336505673</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>18.75084100138341</v>
+        <v>10.84220882653392</v>
       </c>
       <c r="AL13" s="5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM13" s="5" t="n">
-        <v>1.3</v>
+        <v>1.716666666666667</v>
       </c>
       <c r="AN13" s="5" t="n">
-        <v>0</v>
+        <v>0.1799078409944621</v>
       </c>
       <c r="AO13" s="5" t="n">
-        <v>0.1079082363261396</v>
+        <v>0.5759078527107181</v>
       </c>
       <c r="AP13" s="5" t="n">
-        <v>0</v>
+        <v>5.265595346179379</v>
       </c>
       <c r="AQ13" s="5" t="n">
-        <v>4.980380138129521</v>
+        <v>20.12881815299597</v>
       </c>
       <c r="AR13" s="5" t="n">
-        <v>43.56666666666667</v>
+        <v>63.03526666666667</v>
       </c>
       <c r="AS13" s="5" t="n">
-        <v>45.08333333333334</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="AT13" s="5" t="n">
-        <v>38.51537746372311</v>
+        <v>45.7896379485424</v>
       </c>
       <c r="AU13" s="5" t="n">
-        <v>33.88390179261686</v>
+        <v>16.04368253659841</v>
       </c>
       <c r="AV13" s="5" t="n">
-        <v>53.04336605562479</v>
+        <v>43.58478074568644</v>
       </c>
       <c r="AW13" s="5" t="n">
-        <v>45.09502641531263</v>
+        <v>38.30056838975749</v>
       </c>
       <c r="AX13" s="5" t="n">
-        <v>31.55</v>
+        <v>45.45</v>
       </c>
       <c r="AY13" s="5" t="n">
-        <v>29.80076666666667</v>
+        <v>23.43333333333333</v>
       </c>
       <c r="AZ13" s="5" t="n">
-        <v>26.96639094176094</v>
+        <v>33.36307095293761</v>
       </c>
       <c r="BA13" s="5" t="n">
-        <v>22.73451919053936</v>
+        <v>16.77959665852362</v>
       </c>
       <c r="BB13" s="5" t="n">
-        <v>51.28315234566264</v>
+        <v>44.04365802368001</v>
       </c>
       <c r="BC13" s="5" t="n">
-        <v>45.77302210678118</v>
+        <v>42.9634053845555</v>
       </c>
       <c r="BD13" s="5" t="n">
-        <v>69.41061666666666</v>
+        <v>75</v>
       </c>
       <c r="BE13" s="5" t="n">
-        <v>85.78333333333333</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="BF13" s="5" t="n">
-        <v>59.6952680647336</v>
+        <v>67.97543734942298</v>
       </c>
       <c r="BG13" s="5" t="n">
-        <v>68.86227312477148</v>
+        <v>112.1322772301322</v>
       </c>
       <c r="BH13" s="5" t="n">
-        <v>51.60184790007892</v>
+        <v>54.38034987953838</v>
       </c>
       <c r="BI13" s="5" t="n">
-        <v>48.16479177174612</v>
+        <v>46.51719267440379</v>
       </c>
     </row>
     <row r="14">
@@ -2828,32 +2828,32 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
+          <t>16-07-2026</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
           <t>18-07-2026</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>16-07-2026</t>
-        </is>
-      </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>14:14:38</t>
+          <t>14:16:16</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>17:18:32</t>
+          <t>17:36:09</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>16:37:54</t>
+          <t>16:20:34</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>19:38:12</t>
+          <t>20:12:27</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -2862,25 +2862,25 @@
         </is>
       </c>
       <c r="M14" s="7" t="n">
-        <v>143.2666666666667</v>
+        <v>124.3000000000001</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>126.6046070482763</v>
+        <v>136.6906978560236</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>183.89555</v>
+        <v>199.8837333333333</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>48.84353918109128</v>
+        <v>48.73228315978446</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>126.5641866441461</v>
+        <v>137.9070606846193</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>180.3055833333333</v>
+        <v>231.8833333333333</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>49.97551623726486</v>
+        <v>40.29552120062848</v>
       </c>
       <c r="T14" s="7" t="n">
         <v>0</v>
@@ -2901,112 +2901,112 @@
         <v>0</v>
       </c>
       <c r="Z14" s="7" t="n">
-        <v>21.48333333333333</v>
+        <v>26.36886666666667</v>
       </c>
       <c r="AA14" s="7" t="n">
-        <v>27.98333333333333</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="AB14" s="7" t="n">
-        <v>0.237667416199215</v>
+        <v>0.9969610105345994</v>
       </c>
       <c r="AC14" s="7" t="n">
-        <v>0.2139821779699679</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="AD14" s="7" t="n">
-        <v>0.6637724579652243</v>
+        <v>2.26849569942619</v>
       </c>
       <c r="AE14" s="7" t="n">
-        <v>0.4588063375175012</v>
+        <v>0.2959919551202828</v>
       </c>
       <c r="AF14" s="7" t="n">
-        <v>8.303566666666667</v>
+        <v>7.314866666666666</v>
       </c>
       <c r="AG14" s="7" t="n">
-        <v>2.466666666666667</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="AH14" s="7" t="n">
-        <v>0.9134082250757436</v>
+        <v>0.7053124928860509</v>
       </c>
       <c r="AI14" s="7" t="n">
-        <v>1.531702164179549</v>
+        <v>0.9643807655585078</v>
       </c>
       <c r="AJ14" s="7" t="n">
-        <v>6.600114830720688</v>
+        <v>5.785307033142057</v>
       </c>
       <c r="AK14" s="7" t="n">
-        <v>37.25762020977281</v>
+        <v>13.05176975943845</v>
       </c>
       <c r="AL14" s="7" t="n">
-        <v>1.683333333333333</v>
+        <v>0</v>
       </c>
       <c r="AM14" s="7" t="n">
-        <v>0.35</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN14" s="7" t="n">
-        <v>0.3011879778687425</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="7" t="n">
-        <v>0.1671868728596241</v>
+        <v>0.7793029599160757</v>
       </c>
       <c r="AP14" s="7" t="n">
-        <v>10.73541307254924</v>
+        <v>0</v>
       </c>
       <c r="AQ14" s="7" t="n">
-        <v>28.66060677593556</v>
+        <v>4.896144250781626</v>
       </c>
       <c r="AR14" s="7" t="n">
-        <v>48.81666666666667</v>
+        <v>48.73333333333333</v>
       </c>
       <c r="AS14" s="7" t="n">
-        <v>34.15</v>
+        <v>50.65</v>
       </c>
       <c r="AT14" s="7" t="n">
-        <v>38.82861695950649</v>
+        <v>41.44402812668966</v>
       </c>
       <c r="AU14" s="7" t="n">
-        <v>26.10973756311647</v>
+        <v>36.71220944491618</v>
       </c>
       <c r="AV14" s="7" t="n">
-        <v>47.72380370577786</v>
+        <v>51.02547922574651</v>
       </c>
       <c r="AW14" s="7" t="n">
-        <v>45.87362382978004</v>
+        <v>43.4892905566628</v>
       </c>
       <c r="AX14" s="7" t="n">
-        <v>35.13333333333333</v>
+        <v>36.26666666666667</v>
       </c>
       <c r="AY14" s="7" t="n">
-        <v>27.01666666666667</v>
+        <v>34.23333333333333</v>
       </c>
       <c r="AZ14" s="7" t="n">
-        <v>27.71428406489335</v>
+        <v>29.14338787898033</v>
       </c>
       <c r="BA14" s="7" t="n">
-        <v>21.58020657782552</v>
+        <v>25.04052735423578</v>
       </c>
       <c r="BB14" s="7" t="n">
-        <v>47.32989688501711</v>
+        <v>48.21516377037186</v>
       </c>
       <c r="BC14" s="7" t="n">
-        <v>47.92643040109307</v>
+        <v>43.8879739412117</v>
       </c>
       <c r="BD14" s="7" t="n">
-        <v>68.47531666666667</v>
+        <v>81.2</v>
       </c>
       <c r="BE14" s="7" t="n">
-        <v>88.33891666666666</v>
+        <v>109.3</v>
       </c>
       <c r="BF14" s="7" t="n">
-        <v>58.60944240473279</v>
+        <v>64.40100834693297</v>
       </c>
       <c r="BG14" s="7" t="n">
-        <v>76.961371288195</v>
+        <v>74.29364111773266</v>
       </c>
       <c r="BH14" s="7" t="n">
-        <v>51.35524325360015</v>
+        <v>47.58695198049234</v>
       </c>
       <c r="BI14" s="7" t="n">
-        <v>52.27234441549487</v>
+        <v>40.78333455685233</v>
       </c>
     </row>
     <row r="15">
@@ -3035,32 +3035,32 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
+          <t>18-07-2026</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
           <t>16-07-2026</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>20-07-2026</t>
-        </is>
-      </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>14:52:08</t>
+          <t>14:14:38</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>18:17:53</t>
+          <t>18:26:21</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>16:56:44</t>
+          <t>16:37:54</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>20:11:41</t>
+          <t>20:39:30</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -3069,25 +3069,25 @@
         </is>
       </c>
       <c r="M15" s="5" t="n">
-        <v>124.6</v>
+        <v>143.2666666666667</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>123.9185956857711</v>
+        <v>144.8690786295984</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>205.7538833333333</v>
+        <v>251.7108833333333</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>44.92387297676966</v>
+        <v>40.96312925103651</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>123.941936072907</v>
+        <v>143.7246699364842</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>194.9584</v>
+        <v>241.6157666666667</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>42.76203218085404</v>
+        <v>42.34189937201894</v>
       </c>
       <c r="T15" s="5" t="n">
         <v>0</v>
@@ -3108,112 +3108,112 @@
         <v>0</v>
       </c>
       <c r="Z15" s="5" t="n">
-        <v>35.5</v>
+        <v>32.85</v>
       </c>
       <c r="AA15" s="5" t="n">
-        <v>21.38333333333333</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="AB15" s="5" t="n">
-        <v>1.156478673390982</v>
+        <v>0.5585488688475958</v>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>0.1090721560237224</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="AD15" s="5" t="n">
-        <v>1.954611842350956</v>
+        <v>1.020180582370038</v>
       </c>
       <c r="AE15" s="5" t="n">
-        <v>0.3060481384921284</v>
+        <v>0.7042275531456619</v>
       </c>
       <c r="AF15" s="5" t="n">
-        <v>6.983333333333333</v>
+        <v>9.136899999999999</v>
       </c>
       <c r="AG15" s="5" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="AH15" s="5" t="n">
-        <v>0.5163595282581407</v>
+        <v>1.128019155324859</v>
       </c>
       <c r="AI15" s="5" t="n">
-        <v>0.8385213433327759</v>
+        <v>2.057469342854302</v>
       </c>
       <c r="AJ15" s="5" t="n">
-        <v>4.436501913435099</v>
+        <v>7.407452124844482</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>50.31128059996656</v>
+        <v>27.43292457139069</v>
       </c>
       <c r="AL15" s="5" t="n">
-        <v>4.1</v>
+        <v>5.683333333333334</v>
       </c>
       <c r="AM15" s="5" t="n">
-        <v>0</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="AN15" s="5" t="n">
-        <v>0.4394311316082445</v>
+        <v>0.8525702698606122</v>
       </c>
       <c r="AO15" s="5" t="n">
-        <v>0</v>
+        <v>0.270112055303145</v>
       </c>
       <c r="AP15" s="5" t="n">
-        <v>6.43069948694992</v>
+        <v>9.000741851900891</v>
       </c>
       <c r="AQ15" s="5" t="n">
-        <v>0</v>
+        <v>10.02477731021981</v>
       </c>
       <c r="AR15" s="5" t="n">
-        <v>44.28333333333333</v>
+        <v>57.61666666666667</v>
       </c>
       <c r="AS15" s="5" t="n">
-        <v>39.18333333333333</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="AT15" s="5" t="n">
-        <v>35.86032280254005</v>
+        <v>43.55850382048747</v>
       </c>
       <c r="AU15" s="5" t="n">
-        <v>28.21320161975721</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="AV15" s="5" t="n">
-        <v>48.58756570912464</v>
+        <v>45.36031638812696</v>
       </c>
       <c r="AW15" s="5" t="n">
-        <v>43.20183999622542</v>
+        <v>43.26501371597268</v>
       </c>
       <c r="AX15" s="5" t="n">
-        <v>31.21666666666667</v>
+        <v>44.19065</v>
       </c>
       <c r="AY15" s="5" t="n">
-        <v>30.46666666666667</v>
+        <v>34.95</v>
       </c>
       <c r="AZ15" s="5" t="n">
-        <v>24.93604446973648</v>
+        <v>32.43894398667243</v>
       </c>
       <c r="BA15" s="5" t="n">
-        <v>20.93633895165053</v>
+        <v>25.11354425718663</v>
       </c>
       <c r="BB15" s="5" t="n">
-        <v>47.92832893275565</v>
+        <v>44.04408261024324</v>
       </c>
       <c r="BC15" s="5" t="n">
-        <v>41.23130209296603</v>
+        <v>43.11338069903283</v>
       </c>
       <c r="BD15" s="5" t="n">
-        <v>83.67055000000001</v>
+        <v>102.2333333333333</v>
       </c>
       <c r="BE15" s="5" t="n">
-        <v>102.9250666666667</v>
+        <v>121.1324333333333</v>
       </c>
       <c r="BF15" s="5" t="n">
-        <v>61.00995908023722</v>
+        <v>66.33249252840548</v>
       </c>
       <c r="BG15" s="5" t="n">
-        <v>73.8448020021428</v>
+        <v>85.25148709744659</v>
       </c>
       <c r="BH15" s="5" t="n">
-        <v>43.75013125662773</v>
+        <v>38.93005756476358</v>
       </c>
       <c r="BI15" s="5" t="n">
-        <v>43.04770707098789</v>
+        <v>42.22724736133259</v>
       </c>
     </row>
     <row r="16">
@@ -3242,32 +3242,32 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
+          <t>16-07-2026</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
           <t>20-07-2026</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>16-07-2026</t>
-        </is>
-      </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>14:14:55</t>
+          <t>14:52:08</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>17:57:57</t>
+          <t>18:17:53</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>16:37:54</t>
+          <t>16:56:44</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>20:39:30</t>
+          <t>20:11:41</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -3276,25 +3276,25 @@
         </is>
       </c>
       <c r="M16" s="7" t="n">
-        <v>142.9833333333333</v>
+        <v>124.6</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>143.715559613142</v>
+        <v>123.9185956857711</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>223.0419833333333</v>
+        <v>205.7538833333333</v>
       </c>
       <c r="P16" s="7" t="n">
-        <v>46.2946098216972</v>
+        <v>44.92387297676966</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>143.7030109884508</v>
+        <v>123.941936072907</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>241.6157666666667</v>
+        <v>194.9584</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>42.3414520907443</v>
+        <v>42.76203218085404</v>
       </c>
       <c r="T16" s="7" t="n">
         <v>0</v>
@@ -3315,112 +3315,112 @@
         <v>0</v>
       </c>
       <c r="Z16" s="7" t="n">
-        <v>34.49703333333333</v>
+        <v>35.5</v>
       </c>
       <c r="AA16" s="7" t="n">
-        <v>36.98333333333333</v>
+        <v>21.38333333333333</v>
       </c>
       <c r="AB16" s="7" t="n">
-        <v>0.521661623484558</v>
+        <v>1.156478673390982</v>
       </c>
       <c r="AC16" s="7" t="n">
-        <v>0.4340780390083954</v>
+        <v>0.1090721560237224</v>
       </c>
       <c r="AD16" s="7" t="n">
-        <v>0.9073156264376401</v>
+        <v>1.954611842350956</v>
       </c>
       <c r="AE16" s="7" t="n">
-        <v>0.7042275531456619</v>
+        <v>0.3060481384921284</v>
       </c>
       <c r="AF16" s="7" t="n">
-        <v>3.683333333333333</v>
+        <v>6.983333333333333</v>
       </c>
       <c r="AG16" s="7" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="AH16" s="7" t="n">
-        <v>0.5589577464659954</v>
+        <v>0.5163595282581407</v>
       </c>
       <c r="AI16" s="7" t="n">
-        <v>2.037302319652247</v>
+        <v>0.8385213433327759</v>
       </c>
       <c r="AJ16" s="7" t="n">
-        <v>9.105194060079564</v>
+        <v>4.436501913435099</v>
       </c>
       <c r="AK16" s="7" t="n">
-        <v>27.16403092869662</v>
+        <v>50.31128059996656</v>
       </c>
       <c r="AL16" s="7" t="n">
-        <v>5.266666666666667</v>
+        <v>4.1</v>
       </c>
       <c r="AM16" s="7" t="n">
-        <v>1.616666666666667</v>
+        <v>0</v>
       </c>
       <c r="AN16" s="7" t="n">
-        <v>0.3548232692194973</v>
+        <v>0.4394311316082445</v>
       </c>
       <c r="AO16" s="7" t="n">
-        <v>0.270112055303145</v>
+        <v>0</v>
       </c>
       <c r="AP16" s="7" t="n">
-        <v>4.042290408829716</v>
+        <v>6.43069948694992</v>
       </c>
       <c r="AQ16" s="7" t="n">
-        <v>10.02477731021981</v>
+        <v>0</v>
       </c>
       <c r="AR16" s="7" t="n">
-        <v>54.2</v>
+        <v>44.28333333333333</v>
       </c>
       <c r="AS16" s="7" t="n">
-        <v>42.43333333333333</v>
+        <v>39.18333333333333</v>
       </c>
       <c r="AT16" s="7" t="n">
-        <v>43.32090510862054</v>
+        <v>35.86032280254005</v>
       </c>
       <c r="AU16" s="7" t="n">
-        <v>30.59797914468512</v>
+        <v>28.21320161975721</v>
       </c>
       <c r="AV16" s="7" t="n">
-        <v>47.95672152245816</v>
+        <v>48.58756570912464</v>
       </c>
       <c r="AW16" s="7" t="n">
-        <v>43.26501371597268</v>
+        <v>43.20183999622542</v>
       </c>
       <c r="AX16" s="7" t="n">
-        <v>34.92828333333333</v>
+        <v>31.21666666666667</v>
       </c>
       <c r="AY16" s="7" t="n">
-        <v>34.95</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AZ16" s="7" t="n">
-        <v>28.28601681705657</v>
+        <v>24.93604446973648</v>
       </c>
       <c r="BA16" s="7" t="n">
-        <v>25.11354425718663</v>
+        <v>20.93633895165053</v>
       </c>
       <c r="BB16" s="7" t="n">
-        <v>48.58987751636026</v>
+        <v>47.92832893275565</v>
       </c>
       <c r="BC16" s="7" t="n">
-        <v>43.11338069903283</v>
+        <v>41.23130209296603</v>
       </c>
       <c r="BD16" s="7" t="n">
-        <v>90.46666666666667</v>
+        <v>83.67055000000001</v>
       </c>
       <c r="BE16" s="7" t="n">
-        <v>121.1324333333333</v>
+        <v>102.9250666666667</v>
       </c>
       <c r="BF16" s="7" t="n">
-        <v>70.67319504829489</v>
+        <v>61.00995908023722</v>
       </c>
       <c r="BG16" s="7" t="n">
-        <v>85.24999517261531</v>
+        <v>73.8448020021428</v>
       </c>
       <c r="BH16" s="7" t="n">
-        <v>46.8724211816252</v>
+        <v>43.75013125662773</v>
       </c>
       <c r="BI16" s="7" t="n">
-        <v>42.22650837271153</v>
+        <v>43.04770707098789</v>
       </c>
     </row>
     <row r="17">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>26-09-2026</t>
+          <t>20-07-2026</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>14:31:24</t>
+          <t>14:14:55</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>15:43:26</t>
+          <t>17:57:57</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>17:56:14</t>
+          <t>20:39:30</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -3483,25 +3483,25 @@
         </is>
       </c>
       <c r="M17" s="5" t="n">
-        <v>126.5</v>
+        <v>142.9833333333333</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>44.14952488525887</v>
+        <v>143.715559613142</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>72.03223333333334</v>
+        <v>223.0419833333333</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>49.19356496670422</v>
+        <v>46.2946098216972</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>44.09816148211158</v>
+        <v>143.7030109884508</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>78.34408333333334</v>
+        <v>241.6157666666667</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>48.98583197131639</v>
+        <v>42.3414520907443</v>
       </c>
       <c r="T17" s="5" t="n">
         <v>0</v>
@@ -3522,121 +3522,121 @@
         <v>0</v>
       </c>
       <c r="Z17" s="5" t="n">
-        <v>14.45</v>
+        <v>34.49703333333333</v>
       </c>
       <c r="AA17" s="5" t="n">
-        <v>23.88333333333333</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="AB17" s="5" t="n">
-        <v>0.1157287174312111</v>
+        <v>0.521661623484558</v>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>0.1004812886674145</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="AD17" s="5" t="n">
-        <v>0.4805344668423991</v>
+        <v>0.9073156264376401</v>
       </c>
       <c r="AE17" s="5" t="n">
-        <v>0.2524303134701272</v>
+        <v>0.7042275531456619</v>
       </c>
       <c r="AF17" s="5" t="n">
-        <v>4.05</v>
+        <v>3.683333333333333</v>
       </c>
       <c r="AG17" s="5" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="AH17" s="5" t="n">
-        <v>0.1431061962259462</v>
+        <v>0.5589577464659954</v>
       </c>
       <c r="AI17" s="5" t="n">
-        <v>0.8813714304575493</v>
+        <v>2.037302319652247</v>
       </c>
       <c r="AJ17" s="5" t="n">
-        <v>2.120091795939944</v>
+        <v>9.105194060079564</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>32.04987019845634</v>
+        <v>27.16403092869662</v>
       </c>
       <c r="AL17" s="5" t="n">
-        <v>0.95</v>
+        <v>5.266666666666667</v>
       </c>
       <c r="AM17" s="5" t="n">
-        <v>0.35</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="AN17" s="5" t="n">
-        <v>0.04717006116255434</v>
+        <v>0.3548232692194973</v>
       </c>
       <c r="AO17" s="5" t="n">
-        <v>0.1671868728596241</v>
+        <v>0.270112055303145</v>
       </c>
       <c r="AP17" s="5" t="n">
-        <v>2.979161757635011</v>
+        <v>4.042290408829716</v>
       </c>
       <c r="AQ17" s="5" t="n">
-        <v>28.66060677593556</v>
+        <v>10.02477731021981</v>
       </c>
       <c r="AR17" s="5" t="n">
-        <v>19.35811666666667</v>
+        <v>54.2</v>
       </c>
       <c r="AS17" s="5" t="n">
-        <v>11.07741666666667</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="AT17" s="5" t="n">
-        <v>14.57763861092875</v>
+        <v>43.32090510862054</v>
       </c>
       <c r="AU17" s="5" t="n">
-        <v>8.407639114756291</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="AV17" s="5" t="n">
-        <v>45.18302744614747</v>
+        <v>47.95672152245816</v>
       </c>
       <c r="AW17" s="5" t="n">
-        <v>45.53934929642537</v>
+        <v>43.26501371597268</v>
       </c>
       <c r="AX17" s="5" t="n">
-        <v>13.61666666666667</v>
+        <v>34.92828333333333</v>
       </c>
       <c r="AY17" s="5" t="n">
-        <v>9.266666666666667</v>
+        <v>34.95</v>
       </c>
       <c r="AZ17" s="5" t="n">
-        <v>10.50996594053165</v>
+        <v>28.28601681705657</v>
       </c>
       <c r="BA17" s="5" t="n">
-        <v>7.155594247738707</v>
+        <v>25.11354425718663</v>
       </c>
       <c r="BB17" s="5" t="n">
-        <v>46.31074343441117</v>
+        <v>48.58987751636026</v>
       </c>
       <c r="BC17" s="5" t="n">
-        <v>46.33118577672543</v>
+        <v>43.11338069903283</v>
       </c>
       <c r="BD17" s="5" t="n">
-        <v>19.60745</v>
+        <v>90.46666666666667</v>
       </c>
       <c r="BE17" s="5" t="n">
-        <v>32.11666666666667</v>
+        <v>121.1324333333333</v>
       </c>
       <c r="BF17" s="5" t="n">
-        <v>18.75591535897876</v>
+        <v>70.67319504829489</v>
       </c>
       <c r="BG17" s="5" t="n">
-        <v>27.38588852763199</v>
+        <v>85.24999517261531</v>
       </c>
       <c r="BH17" s="5" t="n">
-        <v>57.39425175322266</v>
+        <v>46.8724211816252</v>
       </c>
       <c r="BI17" s="5" t="n">
-        <v>51.16201281757922</v>
+        <v>42.22650837271153</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -3651,37 +3651,37 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Chennai → Pondicherry</t>
+          <t>Pondicherry → Chennai</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>17-07-2026</t>
+          <t>16-07-2026</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>19-07-2026</t>
+          <t>26-09-2026</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>07:59:53</t>
+          <t>14:16:16</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>11:39:50</t>
+          <t>18:52:23</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>11:08:45</t>
+          <t>16:16:08</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>15:37:58</t>
+          <t>21:07:29</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -3690,25 +3690,25 @@
         </is>
       </c>
       <c r="M18" s="7" t="n">
-        <v>188.8666666666667</v>
+        <v>119.8666666666667</v>
       </c>
       <c r="N18" s="7" t="n">
-        <v>146.1177802267258</v>
+        <v>152.2392917821083</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>219.9365833333333</v>
+        <v>276.1022</v>
       </c>
       <c r="P18" s="7" t="n">
-        <v>48.97751792605069</v>
+        <v>40.35574549266031</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>146.2265476173816</v>
+        <v>153.9475902477031</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>269.2166666666666</v>
+        <v>291.3597166666667</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>44.8576416936978</v>
+        <v>36.02192303779674</v>
       </c>
       <c r="T18" s="7" t="n">
         <v>0</v>
@@ -3729,121 +3729,121 @@
         <v>0</v>
       </c>
       <c r="Z18" s="7" t="n">
-        <v>30.18333333333333</v>
+        <v>43.48553333333334</v>
       </c>
       <c r="AA18" s="7" t="n">
-        <v>71.08333333333333</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AB18" s="7" t="n">
-        <v>0.3830658150971378</v>
+        <v>1.349334550099321</v>
       </c>
       <c r="AC18" s="7" t="n">
-        <v>0.5719741256040581</v>
+        <v>0.322941086990129</v>
       </c>
       <c r="AD18" s="7" t="n">
-        <v>0.7614781525950834</v>
+        <v>1.861770267030397</v>
       </c>
       <c r="AE18" s="7" t="n">
-        <v>0.4827917590092871</v>
+        <v>0.7358151349142181</v>
       </c>
       <c r="AF18" s="7" t="n">
-        <v>13.90325</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AG18" s="7" t="n">
-        <v>4.05</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="AH18" s="7" t="n">
-        <v>2.189772290028397</v>
+        <v>0.8562634337407594</v>
       </c>
       <c r="AI18" s="7" t="n">
-        <v>0.5525630686911562</v>
+        <v>0.5256426997626461</v>
       </c>
       <c r="AJ18" s="7" t="n">
-        <v>9.450044946448047</v>
+        <v>5.379665552297964</v>
       </c>
       <c r="AK18" s="7" t="n">
-        <v>8.186119536165277</v>
+        <v>3.148608517713021</v>
       </c>
       <c r="AL18" s="7" t="n">
-        <v>4.233333333333333</v>
+        <v>6.783333333333333</v>
       </c>
       <c r="AM18" s="7" t="n">
-        <v>11.6</v>
+        <v>14.48333333333333</v>
       </c>
       <c r="AN18" s="7" t="n">
-        <v>0.2739207603422623</v>
+        <v>0.6700482500107362</v>
       </c>
       <c r="AO18" s="7" t="n">
-        <v>1.033360466311896</v>
+        <v>1.222282616060936</v>
       </c>
       <c r="AP18" s="7" t="n">
-        <v>3.882341485165922</v>
+        <v>5.926716707711671</v>
       </c>
       <c r="AQ18" s="7" t="n">
-        <v>5.344967929199463</v>
+        <v>5.063541332358309</v>
       </c>
       <c r="AR18" s="7" t="n">
-        <v>46.35</v>
+        <v>55.4</v>
       </c>
       <c r="AS18" s="7" t="n">
-        <v>38.68333333333333</v>
+        <v>52.6</v>
       </c>
       <c r="AT18" s="7" t="n">
-        <v>38.07535235688084</v>
+        <v>44.02574476819412</v>
       </c>
       <c r="AU18" s="7" t="n">
-        <v>27.60990969505806</v>
+        <v>30.18268163700424</v>
       </c>
       <c r="AV18" s="7" t="n">
-        <v>49.28848201537973</v>
+        <v>47.68131202331494</v>
       </c>
       <c r="AW18" s="7" t="n">
-        <v>42.82450448177899</v>
+        <v>34.42891441483373</v>
       </c>
       <c r="AX18" s="7" t="n">
-        <v>31.98333333333333</v>
+        <v>40.21666666666667</v>
       </c>
       <c r="AY18" s="7" t="n">
-        <v>26.81666666666667</v>
+        <v>41.9</v>
       </c>
       <c r="AZ18" s="7" t="n">
-        <v>25.72295810760579</v>
+        <v>31.17572674470658</v>
       </c>
       <c r="BA18" s="7" t="n">
-        <v>19.89292827190748</v>
+        <v>24.79776882222491</v>
       </c>
       <c r="BB18" s="7" t="n">
-        <v>48.25567961822869</v>
+        <v>46.51165200204877</v>
       </c>
       <c r="BC18" s="7" t="n">
-        <v>44.50872702229143</v>
+        <v>35.5099314876729</v>
       </c>
       <c r="BD18" s="7" t="n">
-        <v>93.28333333333333</v>
+        <v>120.6666666666667</v>
       </c>
       <c r="BE18" s="7" t="n">
-        <v>116.9833333333333</v>
+        <v>146.0263833333333</v>
       </c>
       <c r="BF18" s="7" t="n">
-        <v>79.47271089677133</v>
+        <v>74.16217403535677</v>
       </c>
       <c r="BG18" s="7" t="n">
-        <v>96.56581198980894</v>
+        <v>96.89627338566024</v>
       </c>
       <c r="BH18" s="7" t="n">
-        <v>51.11698396076055</v>
+        <v>36.8762191336028</v>
       </c>
       <c r="BI18" s="7" t="n">
-        <v>49.52798449398949</v>
+        <v>39.81319177006905</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -3858,37 +3858,37 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Chennai → Pondicherry</t>
+          <t>Pondicherry → Chennai</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>19-07-2026</t>
+          <t>26-09-2026</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>17-07-2026</t>
+          <t>16-07-2026</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>09:26:56</t>
+          <t>14:31:24</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>12:33:03</t>
+          <t>18:34:00</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>11:43:51</t>
+          <t>16:37:54</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>15:25:00</t>
+          <t>20:40:25</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -3897,25 +3897,25 @@
         </is>
       </c>
       <c r="M19" s="5" t="n">
-        <v>136.9166666666667</v>
+        <v>126.5</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>141.7178099447946</v>
+        <v>145.5987620683535</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>186.11555</v>
+        <v>242.5876</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>48.97984764694002</v>
+        <v>44.70287136285296</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>141.7137294264382</v>
+        <v>143.8194371210736</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>221.15</v>
+        <v>242.5281833333333</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>44.83512073701105</v>
+        <v>42.18577398047646</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>0</v>
@@ -3936,112 +3936,112 @@
         <v>0</v>
       </c>
       <c r="Z19" s="5" t="n">
-        <v>8.933333333333334</v>
+        <v>35.1</v>
       </c>
       <c r="AA19" s="5" t="n">
-        <v>31.8</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="AB19" s="5" t="n">
-        <v>0.2591759316479205</v>
+        <v>0.1862366457606098</v>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>0.2215609005542024</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="AD19" s="5" t="n">
-        <v>1.740733869277078</v>
+        <v>0.318353240616427</v>
       </c>
       <c r="AE19" s="5" t="n">
-        <v>0.4180394350079291</v>
+        <v>0.7042275531456619</v>
       </c>
       <c r="AF19" s="5" t="n">
-        <v>4.777933333333333</v>
+        <v>12.7</v>
       </c>
       <c r="AG19" s="5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH19" s="5" t="n">
-        <v>0.7197084907042335</v>
+        <v>0.2864416579452221</v>
       </c>
       <c r="AI19" s="5" t="n">
-        <v>0</v>
+        <v>2.031482381418694</v>
       </c>
       <c r="AJ19" s="5" t="n">
-        <v>9.037905393319429</v>
+        <v>1.353267675331758</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>0</v>
+        <v>27.08643175224925</v>
       </c>
       <c r="AL19" s="5" t="n">
-        <v>0</v>
+        <v>3.933333333333333</v>
       </c>
       <c r="AM19" s="5" t="n">
-        <v>1.5</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="AN19" s="5" t="n">
-        <v>0</v>
+        <v>0.3063808251647893</v>
       </c>
       <c r="AO19" s="5" t="n">
-        <v>0.1164747371577703</v>
+        <v>0.270112055303145</v>
       </c>
       <c r="AP19" s="5" t="n">
-        <v>0</v>
+        <v>4.673605807598481</v>
       </c>
       <c r="AQ19" s="5" t="n">
-        <v>4.658989486310812</v>
+        <v>10.02477731021981</v>
       </c>
       <c r="AR19" s="5" t="n">
-        <v>45.07095</v>
+        <v>68.01666666666667</v>
       </c>
       <c r="AS19" s="5" t="n">
-        <v>30.46666666666667</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="AT19" s="5" t="n">
-        <v>36.70010973267537</v>
+        <v>51.04021071573327</v>
       </c>
       <c r="AU19" s="5" t="n">
-        <v>21.5632715446163</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="AV19" s="5" t="n">
-        <v>48.85644930849077</v>
+        <v>45.02444464019597</v>
       </c>
       <c r="AW19" s="5" t="n">
-        <v>42.46596146642159</v>
+        <v>43.26501371597268</v>
       </c>
       <c r="AX19" s="5" t="n">
-        <v>34.96666666666667</v>
+        <v>51.25311666666666</v>
       </c>
       <c r="AY19" s="5" t="n">
-        <v>23</v>
+        <v>34.95</v>
       </c>
       <c r="AZ19" s="5" t="n">
-        <v>27.29337511764809</v>
+        <v>36.75236971798009</v>
       </c>
       <c r="BA19" s="5" t="n">
-        <v>17.07426318972899</v>
+        <v>25.11354425718663</v>
       </c>
       <c r="BB19" s="5" t="n">
-        <v>46.8332461503971</v>
+        <v>43.02454809568599</v>
       </c>
       <c r="BC19" s="5" t="n">
-        <v>44.5415561471191</v>
+        <v>43.11338069903283</v>
       </c>
       <c r="BD19" s="5" t="n">
-        <v>92.36666666666666</v>
+        <v>71.58448333333334</v>
       </c>
       <c r="BE19" s="5" t="n">
-        <v>134.3833333333333</v>
+        <v>122.04485</v>
       </c>
       <c r="BF19" s="5" t="n">
-        <v>76.745440672119</v>
+        <v>57.02712250576948</v>
       </c>
       <c r="BG19" s="5" t="n">
-        <v>102.738159054381</v>
+        <v>85.37224124347163</v>
       </c>
       <c r="BH19" s="5" t="n">
-        <v>49.85268610964064</v>
+        <v>47.79845004137771</v>
       </c>
       <c r="BI19" s="5" t="n">
-        <v>45.87093793820807</v>
+        <v>41.97091867955344</v>
       </c>
     </row>
     <row r="20">
@@ -4070,32 +4070,32 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>17-07-2026</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>17-07-2026</t>
+          <t>19-07-2026</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>14:13:59</t>
+          <t>07:59:53</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>17:55:07</t>
+          <t>11:39:50</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>11:43:51</t>
+          <t>11:08:45</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>15:25:00</t>
+          <t>15:37:58</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -4104,25 +4104,25 @@
         </is>
       </c>
       <c r="M20" s="7" t="n">
-        <v>150.1333333333333</v>
+        <v>188.8666666666667</v>
       </c>
       <c r="N20" s="7" t="n">
-        <v>141.8317368861638</v>
+        <v>146.1177802267258</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>221.1224333333333</v>
+        <v>219.9365833333333</v>
       </c>
       <c r="P20" s="7" t="n">
-        <v>49.27030586470386</v>
+        <v>48.97751792605069</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>141.6733980516045</v>
+        <v>146.2265476173816</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>221.15</v>
+        <v>269.2166666666666</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>44.82234079251659</v>
+        <v>44.8576416936978</v>
       </c>
       <c r="T20" s="7" t="n">
         <v>0</v>
@@ -4143,121 +4143,121 @@
         <v>0</v>
       </c>
       <c r="Z20" s="7" t="n">
-        <v>30.46666666666667</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="AA20" s="7" t="n">
-        <v>31.8</v>
+        <v>71.08333333333333</v>
       </c>
       <c r="AB20" s="7" t="n">
-        <v>0.4844248901091631</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="AC20" s="7" t="n">
-        <v>0.2215609005542024</v>
+        <v>0.5719741256040581</v>
       </c>
       <c r="AD20" s="7" t="n">
-        <v>0.9540096304119186</v>
+        <v>0.7614781525950834</v>
       </c>
       <c r="AE20" s="7" t="n">
-        <v>0.4180394350079291</v>
+        <v>0.4827917590092871</v>
       </c>
       <c r="AF20" s="7" t="n">
-        <v>18.98408333333333</v>
+        <v>13.90325</v>
       </c>
       <c r="AG20" s="7" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AH20" s="7" t="n">
-        <v>0.3753728936893338</v>
+        <v>2.189772290028397</v>
       </c>
       <c r="AI20" s="7" t="n">
-        <v>0</v>
+        <v>0.5525630686911562</v>
       </c>
       <c r="AJ20" s="7" t="n">
-        <v>1.186381940381286</v>
+        <v>9.450044946448047</v>
       </c>
       <c r="AK20" s="7" t="n">
-        <v>0</v>
+        <v>8.186119536165277</v>
       </c>
       <c r="AL20" s="7" t="n">
-        <v>2.3</v>
+        <v>4.233333333333333</v>
       </c>
       <c r="AM20" s="7" t="n">
-        <v>1.5</v>
+        <v>11.6</v>
       </c>
       <c r="AN20" s="7" t="n">
-        <v>0.185676926950206</v>
+        <v>0.2739207603422623</v>
       </c>
       <c r="AO20" s="7" t="n">
-        <v>0.1164747371577703</v>
+        <v>1.033360466311896</v>
       </c>
       <c r="AP20" s="7" t="n">
-        <v>4.843745920440157</v>
+        <v>3.882341485165922</v>
       </c>
       <c r="AQ20" s="7" t="n">
-        <v>4.658989486310812</v>
+        <v>5.344967929199463</v>
       </c>
       <c r="AR20" s="7" t="n">
-        <v>58.60501666666666</v>
+        <v>46.35</v>
       </c>
       <c r="AS20" s="7" t="n">
-        <v>30.46666666666667</v>
+        <v>38.68333333333333</v>
       </c>
       <c r="AT20" s="7" t="n">
-        <v>43.70509198694462</v>
+        <v>38.07535235688084</v>
       </c>
       <c r="AU20" s="7" t="n">
-        <v>21.5665214603954</v>
+        <v>27.60990969505806</v>
       </c>
       <c r="AV20" s="7" t="n">
-        <v>44.74541034826105</v>
+        <v>49.28848201537973</v>
       </c>
       <c r="AW20" s="7" t="n">
-        <v>42.47236173819663</v>
+        <v>42.82450448177899</v>
       </c>
       <c r="AX20" s="7" t="n">
-        <v>41.15</v>
+        <v>31.98333333333333</v>
       </c>
       <c r="AY20" s="7" t="n">
-        <v>23</v>
+        <v>26.81666666666667</v>
       </c>
       <c r="AZ20" s="7" t="n">
-        <v>31.31100557837641</v>
+        <v>25.72295810760579</v>
       </c>
       <c r="BA20" s="7" t="n">
-        <v>17.03068189911616</v>
+        <v>19.89292827190748</v>
       </c>
       <c r="BB20" s="7" t="n">
-        <v>45.65395710091336</v>
+        <v>48.25567961822869</v>
       </c>
       <c r="BC20" s="7" t="n">
-        <v>44.42786582378129</v>
+        <v>44.50872702229143</v>
       </c>
       <c r="BD20" s="7" t="n">
-        <v>69.61666666666666</v>
+        <v>93.28333333333333</v>
       </c>
       <c r="BE20" s="7" t="n">
-        <v>134.3833333333333</v>
+        <v>116.9833333333333</v>
       </c>
       <c r="BF20" s="7" t="n">
-        <v>65.77016461009407</v>
+        <v>79.47271089677133</v>
       </c>
       <c r="BG20" s="7" t="n">
-        <v>102.738159054381</v>
+        <v>96.56581198980894</v>
       </c>
       <c r="BH20" s="7" t="n">
-        <v>56.68484381047131</v>
+        <v>51.11698396076055</v>
       </c>
       <c r="BI20" s="7" t="n">
-        <v>45.87093793820807</v>
+        <v>49.52798449398949</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>PAIR_021</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -4272,37 +4272,37 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Pondicherry → Chennai</t>
+          <t>Chennai → Pondicherry</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>18-07-2026</t>
+          <t>19-07-2026</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>17-07-2026</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>14:59:13</t>
+          <t>09:26:56</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>17:18:32</t>
+          <t>12:33:03</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>16:56:44</t>
+          <t>11:43:51</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>19:26:14</t>
+          <t>15:25:00</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -4311,25 +4311,25 @@
         </is>
       </c>
       <c r="M21" s="5" t="n">
-        <v>117.5166666666667</v>
+        <v>136.9166666666667</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>106.7510397234517</v>
+        <v>141.7178099447946</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>139.3205333333333</v>
+        <v>186.11555</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>51.58938782842431</v>
+        <v>48.97984764694002</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>106.7303536725813</v>
+        <v>141.7137294264382</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>149.51085</v>
+        <v>221.15</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>49.91426587048593</v>
+        <v>44.83512073701105</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>0</v>
@@ -4350,121 +4350,121 @@
         <v>0</v>
       </c>
       <c r="Z21" s="5" t="n">
-        <v>15.21666666666667</v>
+        <v>8.933333333333334</v>
       </c>
       <c r="AA21" s="5" t="n">
-        <v>21.38333333333333</v>
+        <v>31.8</v>
       </c>
       <c r="AB21" s="5" t="n">
-        <v>0.1119981388984077</v>
+        <v>0.2591759316479205</v>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>0.1090721560237224</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="AD21" s="5" t="n">
-        <v>0.4416136911656819</v>
+        <v>1.740733869277078</v>
       </c>
       <c r="AE21" s="5" t="n">
-        <v>0.3060481384921284</v>
+        <v>0.4180394350079291</v>
       </c>
       <c r="AF21" s="5" t="n">
-        <v>0.42855</v>
+        <v>4.777933333333333</v>
       </c>
       <c r="AG21" s="5" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="AH21" s="5" t="n">
-        <v>0.3001436458890005</v>
+        <v>0.7197084907042335</v>
       </c>
       <c r="AI21" s="5" t="n">
-        <v>0.724686338784539</v>
+        <v>0</v>
       </c>
       <c r="AJ21" s="5" t="n">
-        <v>42.02221153503682</v>
+        <v>9.037905393319429</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>52.1774163924868</v>
+        <v>0</v>
       </c>
       <c r="AL21" s="5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM21" s="5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN21" s="5" t="n">
-        <v>0.1868101281681779</v>
+        <v>0</v>
       </c>
       <c r="AO21" s="5" t="n">
-        <v>0</v>
+        <v>0.1164747371577703</v>
       </c>
       <c r="AP21" s="5" t="n">
-        <v>8.302672363030128</v>
+        <v>0</v>
       </c>
       <c r="AQ21" s="5" t="n">
-        <v>0</v>
+        <v>4.658989486310812</v>
       </c>
       <c r="AR21" s="5" t="n">
-        <v>41.28333333333333</v>
+        <v>45.07095</v>
       </c>
       <c r="AS21" s="5" t="n">
-        <v>31.31666666666667</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AT21" s="5" t="n">
-        <v>33.31093548904284</v>
+        <v>36.70010973267537</v>
       </c>
       <c r="AU21" s="5" t="n">
-        <v>23.85603505749816</v>
+        <v>21.5632715446163</v>
       </c>
       <c r="AV21" s="5" t="n">
-        <v>48.41314806643288</v>
+        <v>48.85644930849077</v>
       </c>
       <c r="AW21" s="5" t="n">
-        <v>45.70608100425405</v>
+        <v>42.46596146642159</v>
       </c>
       <c r="AX21" s="5" t="n">
-        <v>28.96666666666667</v>
+        <v>34.96666666666667</v>
       </c>
       <c r="AY21" s="5" t="n">
-        <v>22.95</v>
+        <v>23</v>
       </c>
       <c r="AZ21" s="5" t="n">
-        <v>23.64150595454553</v>
+        <v>27.29337511764809</v>
       </c>
       <c r="BA21" s="5" t="n">
-        <v>16.88692331213</v>
+        <v>17.07426318972899</v>
       </c>
       <c r="BB21" s="5" t="n">
-        <v>48.96974766188947</v>
+        <v>46.8332461503971</v>
       </c>
       <c r="BC21" s="5" t="n">
-        <v>44.14881911667975</v>
+        <v>44.5415561471191</v>
       </c>
       <c r="BD21" s="5" t="n">
-        <v>52.07531666666667</v>
+        <v>92.36666666666666</v>
       </c>
       <c r="BE21" s="5" t="n">
-        <v>73.02751666666667</v>
+        <v>134.3833333333333</v>
       </c>
       <c r="BF21" s="5" t="n">
-        <v>49.1996463669077</v>
+        <v>76.745440672119</v>
       </c>
       <c r="BG21" s="5" t="n">
-        <v>65.15363680814482</v>
+        <v>102.738159054381</v>
       </c>
       <c r="BH21" s="5" t="n">
-        <v>56.68671783428672</v>
+        <v>49.85268610964064</v>
       </c>
       <c r="BI21" s="5" t="n">
-        <v>53.53075644530369</v>
+        <v>45.87093793820807</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>PAIR_022</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -4479,37 +4479,37 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Pondicherry → Chennai</t>
+          <t>Chennai → Pondicherry</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>17-07-2026</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>18-07-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>14:14:55</t>
+          <t>07:39:02</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>17:01:15</t>
+          <t>11:34:46</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>16:20:34</t>
+          <t>14:27:10</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>19:28:38</t>
+          <t>19:12:44</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -4518,25 +4518,25 @@
         </is>
       </c>
       <c r="M22" s="7" t="n">
-        <v>125.6500000000001</v>
+        <v>408.1333333333333</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>126.5111630773044</v>
+        <v>153.5802936448807</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>166.3452166666667</v>
+        <v>235.7315</v>
       </c>
       <c r="P22" s="7" t="n">
-        <v>54.3571101011709</v>
+        <v>47.72215002408557</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>126.4609732010443</v>
+        <v>153.5880362119665</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>188.0674333333333</v>
+        <v>285.5666666666667</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>46.52817854574852</v>
+        <v>41.36278147867761</v>
       </c>
       <c r="T22" s="7" t="n">
         <v>0</v>
@@ -4557,328 +4557,328 @@
         <v>0</v>
       </c>
       <c r="Z22" s="7" t="n">
-        <v>23.84703333333334</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="AA22" s="7" t="n">
-        <v>23.71666666666667</v>
+        <v>48.18333333333333</v>
       </c>
       <c r="AB22" s="7" t="n">
-        <v>0.1926372453796382</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="AC22" s="7" t="n">
-        <v>0.1169990422600451</v>
+        <v>0.6526929809004927</v>
       </c>
       <c r="AD22" s="7" t="n">
-        <v>0.4846822898772156</v>
+        <v>0.7614781525950834</v>
       </c>
       <c r="AE22" s="7" t="n">
-        <v>0.2959919551202828</v>
+        <v>0.8127619270985035</v>
       </c>
       <c r="AF22" s="7" t="n">
-        <v>3.683333333333333</v>
+        <v>15.93333333333333</v>
       </c>
       <c r="AG22" s="7" t="n">
-        <v>2.383333333333333</v>
+        <v>17.66666666666667</v>
       </c>
       <c r="AH22" s="7" t="n">
-        <v>0.5589577464659954</v>
+        <v>2.383435777694972</v>
       </c>
       <c r="AI22" s="7" t="n">
-        <v>0.7431465466183387</v>
+        <v>1.46713538845297</v>
       </c>
       <c r="AJ22" s="7" t="n">
-        <v>9.105194060079564</v>
+        <v>8.975281171236297</v>
       </c>
       <c r="AK22" s="7" t="n">
-        <v>18.70858439039175</v>
+        <v>4.982723960783671</v>
       </c>
       <c r="AL22" s="7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM22" s="7" t="n">
-        <v>1.3</v>
+        <v>9.9</v>
       </c>
       <c r="AN22" s="7" t="n">
-        <v>0</v>
+        <v>0.2046142102738726</v>
       </c>
       <c r="AO22" s="7" t="n">
-        <v>0.1079082363261396</v>
+        <v>1.3169091629821</v>
       </c>
       <c r="AP22" s="7" t="n">
-        <v>0</v>
+        <v>5.846120293539217</v>
       </c>
       <c r="AQ22" s="7" t="n">
-        <v>4.980380138129521</v>
+        <v>7.981267654436969</v>
       </c>
       <c r="AR22" s="7" t="n">
-        <v>44.66666666666666</v>
+        <v>50.65</v>
       </c>
       <c r="AS22" s="7" t="n">
-        <v>45.08333333333334</v>
+        <v>51.03333333333333</v>
       </c>
       <c r="AT22" s="7" t="n">
-        <v>38.02172328104655</v>
+        <v>40.28614742330923</v>
       </c>
       <c r="AU22" s="7" t="n">
-        <v>33.88390179261686</v>
+        <v>32.22664079654989</v>
       </c>
       <c r="AV22" s="7" t="n">
-        <v>51.07395664618194</v>
+        <v>47.72297819148181</v>
       </c>
       <c r="AW22" s="7" t="n">
-        <v>45.09502641531263</v>
+        <v>37.88893104754396</v>
       </c>
       <c r="AX22" s="7" t="n">
-        <v>27.98333333333333</v>
+        <v>37.05954999999999</v>
       </c>
       <c r="AY22" s="7" t="n">
-        <v>29.80076666666667</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="AZ22" s="7" t="n">
-        <v>24.42883704029827</v>
+        <v>27.90182873497321</v>
       </c>
       <c r="BA22" s="7" t="n">
-        <v>22.74674445845141</v>
+        <v>24.26414905968165</v>
       </c>
       <c r="BB22" s="7" t="n">
-        <v>52.37868573262286</v>
+        <v>45.1735038363497</v>
       </c>
       <c r="BC22" s="7" t="n">
-        <v>45.79763610691506</v>
+        <v>39.20598591330966</v>
       </c>
       <c r="BD22" s="7" t="n">
-        <v>66.16485</v>
+        <v>99.80528333333334</v>
       </c>
       <c r="BE22" s="7" t="n">
-        <v>85.78333333333333</v>
+        <v>121.65</v>
       </c>
       <c r="BF22" s="7" t="n">
-        <v>63.30900776411389</v>
+        <v>82.42120168353226</v>
       </c>
       <c r="BG22" s="7" t="n">
-        <v>68.86227312477148</v>
+        <v>93.6605088233994</v>
       </c>
       <c r="BH22" s="7" t="n">
-        <v>57.41024827906107</v>
+        <v>49.54920156376426</v>
       </c>
       <c r="BI22" s="7" t="n">
-        <v>48.16479177174612</v>
+        <v>46.19507216937085</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>PAIR_022</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Chennai ↔ Pondicherry</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Chennai → Pondicherry</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>17-07-2026</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>14:13:59</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>17:55:07</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>11:43:51</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>15:25:00</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>150.1333333333333</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>141.8317368861638</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>221.1224333333333</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>49.27030586470386</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>141.6733980516045</v>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>221.15</v>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>44.82234079251659</v>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AA23" s="5" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AB23" s="5" t="n">
+        <v>0.4844248901091631</v>
+      </c>
+      <c r="AC23" s="5" t="n">
+        <v>0.2215609005542024</v>
+      </c>
+      <c r="AD23" s="5" t="n">
+        <v>0.9540096304119186</v>
+      </c>
+      <c r="AE23" s="5" t="n">
+        <v>0.4180394350079291</v>
+      </c>
+      <c r="AF23" s="5" t="n">
+        <v>18.98408333333333</v>
+      </c>
+      <c r="AG23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="5" t="n">
+        <v>0.3753728936893338</v>
+      </c>
+      <c r="AI23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="5" t="n">
+        <v>1.186381940381286</v>
+      </c>
+      <c r="AK23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM23" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN23" s="5" t="n">
+        <v>0.185676926950206</v>
+      </c>
+      <c r="AO23" s="5" t="n">
+        <v>0.1164747371577703</v>
+      </c>
+      <c r="AP23" s="5" t="n">
+        <v>4.843745920440157</v>
+      </c>
+      <c r="AQ23" s="5" t="n">
+        <v>4.658989486310812</v>
+      </c>
+      <c r="AR23" s="5" t="n">
+        <v>58.60501666666666</v>
+      </c>
+      <c r="AS23" s="5" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AT23" s="5" t="n">
+        <v>43.70509198694462</v>
+      </c>
+      <c r="AU23" s="5" t="n">
+        <v>21.5665214603954</v>
+      </c>
+      <c r="AV23" s="5" t="n">
+        <v>44.74541034826105</v>
+      </c>
+      <c r="AW23" s="5" t="n">
+        <v>42.47236173819663</v>
+      </c>
+      <c r="AX23" s="5" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="AY23" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>PAIR_023</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>NONSTRICT</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Chennai ↔ Pondicherry</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Pondicherry → Chennai</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>26-09-2026</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>18-07-2026</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>14:31:24</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>15:43:26</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>16:20:34</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>17:41:38</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v>109.1666666666667</v>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v>44.14425672881129</v>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v>72.03223333333334</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>49.18766031137466</v>
-      </c>
-      <c r="Q23" s="5" t="n">
-        <v>44.07790624114242</v>
-      </c>
-      <c r="R23" s="5" t="n">
-        <v>81.07328333333334</v>
-      </c>
-      <c r="S23" s="5" t="n">
-        <v>46.38866788428458</v>
-      </c>
-      <c r="T23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="5" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="AA23" s="5" t="n">
-        <v>23.71666666666667</v>
-      </c>
-      <c r="AB23" s="5" t="n">
-        <v>0.1157287174312111</v>
-      </c>
-      <c r="AC23" s="5" t="n">
-        <v>0.1169990422600451</v>
-      </c>
-      <c r="AD23" s="5" t="n">
-        <v>0.4805344668423991</v>
-      </c>
-      <c r="AE23" s="5" t="n">
-        <v>0.2959919551202828</v>
-      </c>
-      <c r="AF23" s="5" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AG23" s="5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AH23" s="5" t="n">
-        <v>0.1431061962259462</v>
-      </c>
-      <c r="AI23" s="5" t="n">
-        <v>0.2344720787358082</v>
-      </c>
-      <c r="AJ23" s="5" t="n">
-        <v>2.120091795939944</v>
-      </c>
-      <c r="AK23" s="5" t="n">
-        <v>17.58540590518561</v>
-      </c>
-      <c r="AL23" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AM23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="5" t="n">
-        <v>0.04717006116255434</v>
-      </c>
-      <c r="AO23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" s="5" t="n">
-        <v>2.979161757635011</v>
-      </c>
-      <c r="AQ23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" s="5" t="n">
-        <v>19.35811666666667</v>
-      </c>
-      <c r="AS23" s="5" t="n">
-        <v>16.17328333333333</v>
-      </c>
-      <c r="AT23" s="5" t="n">
-        <v>14.5716785028715</v>
-      </c>
-      <c r="AU23" s="5" t="n">
-        <v>11.42860053715295</v>
-      </c>
-      <c r="AV23" s="5" t="n">
-        <v>45.16455423981274</v>
-      </c>
-      <c r="AW23" s="5" t="n">
-        <v>42.39807206097157</v>
-      </c>
-      <c r="AX23" s="5" t="n">
-        <v>13.61666666666667</v>
-      </c>
-      <c r="AY23" s="5" t="n">
-        <v>10.23333333333333</v>
-      </c>
       <c r="AZ23" s="5" t="n">
-        <v>10.50996594053165</v>
+        <v>31.31100557837641</v>
       </c>
       <c r="BA23" s="5" t="n">
-        <v>7.866765487152254</v>
+        <v>17.03068189911616</v>
       </c>
       <c r="BB23" s="5" t="n">
-        <v>46.31074343441117</v>
+        <v>45.65395710091336</v>
       </c>
       <c r="BC23" s="5" t="n">
-        <v>46.12435790512723</v>
+        <v>44.42786582378129</v>
       </c>
       <c r="BD23" s="5" t="n">
-        <v>19.60745</v>
+        <v>69.61666666666666</v>
       </c>
       <c r="BE23" s="5" t="n">
-        <v>30.15</v>
+        <v>134.3833333333333</v>
       </c>
       <c r="BF23" s="5" t="n">
-        <v>18.75660731058842</v>
+        <v>65.77016461009407</v>
       </c>
       <c r="BG23" s="5" t="n">
-        <v>24.43106909584137</v>
+        <v>102.738159054381</v>
       </c>
       <c r="BH23" s="5" t="n">
-        <v>57.39636916760238</v>
+        <v>56.68484381047131</v>
       </c>
       <c r="BI23" s="5" t="n">
-        <v>48.61904297679875</v>
+        <v>45.87093793820807</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>PAIR_025</t>
+          <t>PAIR_024</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -4893,37 +4893,37 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Chennai → Pondicherry</t>
+          <t>Pondicherry → Chennai</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>18-07-2026</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>19-07-2026</t>
+          <t>20-07-2026</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>13:56:09</t>
+          <t>14:59:13</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>18:11:54</t>
+          <t>18:26:21</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>11:08:45</t>
+          <t>16:56:44</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>15:34:22</t>
+          <t>20:11:15</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -4932,25 +4932,25 @@
         </is>
       </c>
       <c r="M24" s="7" t="n">
-        <v>167.4</v>
+        <v>117.5166666666667</v>
       </c>
       <c r="N24" s="7" t="n">
-        <v>145.9773325040056</v>
+        <v>125.021511754306</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>255.7438833333333</v>
+        <v>207.1358666666667</v>
       </c>
       <c r="P24" s="7" t="n">
-        <v>47.2452299004206</v>
+        <v>41.52158885696085</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>145.8893363990339</v>
+        <v>123.8871365945718</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>265.6299833333333</v>
+        <v>194.5326</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>45.59497163487288</v>
+        <v>42.83521220753777</v>
       </c>
       <c r="T24" s="7" t="n">
         <v>0</v>
@@ -4971,121 +4971,121 @@
         <v>0</v>
       </c>
       <c r="Z24" s="7" t="n">
-        <v>45.16666666666666</v>
+        <v>26.58333333333333</v>
       </c>
       <c r="AA24" s="7" t="n">
-        <v>71.08333333333333</v>
+        <v>21.38333333333333</v>
       </c>
       <c r="AB24" s="7" t="n">
-        <v>0.6992727007011277</v>
+        <v>0.4328795915467885</v>
       </c>
       <c r="AC24" s="7" t="n">
-        <v>0.5752841088710083</v>
+        <v>0.1090721560237224</v>
       </c>
       <c r="AD24" s="7" t="n">
-        <v>0.9289231448428267</v>
+        <v>0.9770323069394602</v>
       </c>
       <c r="AE24" s="7" t="n">
-        <v>0.4855856487539578</v>
+        <v>0.3060481384921284</v>
       </c>
       <c r="AF24" s="7" t="n">
-        <v>26.67068333333333</v>
+        <v>1.261883333333333</v>
       </c>
       <c r="AG24" s="7" t="n">
-        <v>4.05</v>
+        <v>1</v>
       </c>
       <c r="AH24" s="7" t="n">
-        <v>0.4662856779261432</v>
+        <v>0.5147545761381157</v>
       </c>
       <c r="AI24" s="7" t="n">
-        <v>0.5525630686911562</v>
+        <v>0.8772249545701249</v>
       </c>
       <c r="AJ24" s="7" t="n">
-        <v>1.04898477200254</v>
+        <v>24.47553886515152</v>
       </c>
       <c r="AK24" s="7" t="n">
-        <v>8.186119536165277</v>
+        <v>52.6334972742075</v>
       </c>
       <c r="AL24" s="7" t="n">
-        <v>2.883333333333333</v>
+        <v>5.35</v>
       </c>
       <c r="AM24" s="7" t="n">
-        <v>7.683333333333334</v>
+        <v>0</v>
       </c>
       <c r="AN24" s="7" t="n">
-        <v>0.2514853038814903</v>
+        <v>0.7381924201600477</v>
       </c>
       <c r="AO24" s="7" t="n">
-        <v>0.6833899734934139</v>
+        <v>0</v>
       </c>
       <c r="AP24" s="7" t="n">
-        <v>5.233220196377834</v>
+        <v>8.278793497122031</v>
       </c>
       <c r="AQ24" s="7" t="n">
-        <v>5.336667905805401</v>
+        <v>0</v>
       </c>
       <c r="AR24" s="7" t="n">
-        <v>61.42319999999999</v>
+        <v>50.08333333333334</v>
       </c>
       <c r="AS24" s="7" t="n">
-        <v>38.68333333333333</v>
+        <v>39.18333333333333</v>
       </c>
       <c r="AT24" s="7" t="n">
-        <v>44.94924920648065</v>
+        <v>38.04082235002382</v>
       </c>
       <c r="AU24" s="7" t="n">
-        <v>27.60990969505806</v>
+        <v>28.21320161975721</v>
       </c>
       <c r="AV24" s="7" t="n">
-        <v>43.90775720556466</v>
+        <v>45.57303176708344</v>
       </c>
       <c r="AW24" s="7" t="n">
-        <v>42.82450448177899</v>
+        <v>43.20183999622542</v>
       </c>
       <c r="AX24" s="7" t="n">
-        <v>44.01666666666667</v>
+        <v>38.02398333333333</v>
       </c>
       <c r="AY24" s="7" t="n">
-        <v>26.81666666666667</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AZ24" s="7" t="n">
-        <v>32.63164533881391</v>
+        <v>28.34973504817535</v>
       </c>
       <c r="BA24" s="7" t="n">
-        <v>19.89292827190748</v>
+        <v>20.93633895165053</v>
       </c>
       <c r="BB24" s="7" t="n">
-        <v>44.48084938270733</v>
+        <v>44.73450579806485</v>
       </c>
       <c r="BC24" s="7" t="n">
-        <v>44.50872702229143</v>
+        <v>41.23130209296603</v>
       </c>
       <c r="BD24" s="7" t="n">
-        <v>75.58333333333333</v>
+        <v>85.83333333333333</v>
       </c>
       <c r="BE24" s="7" t="n">
-        <v>117.3133166666667</v>
+        <v>102.4992666666667</v>
       </c>
       <c r="BF24" s="7" t="n">
-        <v>66.97939427620221</v>
+        <v>56.94512776826193</v>
       </c>
       <c r="BG24" s="7" t="n">
-        <v>96.5752612810128</v>
+        <v>73.75129891257018</v>
       </c>
       <c r="BH24" s="7" t="n">
-        <v>53.16997120051334</v>
+        <v>39.8063029059695</v>
       </c>
       <c r="BI24" s="7" t="n">
-        <v>49.39350315467823</v>
+        <v>43.17180091780374</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>PAIR_027</t>
+          <t>PAIR_025</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Maduravoyal ↔ Silk Board</t>
+          <t>Chennai ↔ Pondicherry</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Silk Board → Maduravoyal</t>
+          <t>Pondicherry → Chennai</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -5110,27 +5110,27 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>29-07-2026</t>
+          <t>18-07-2026</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>00:03:01</t>
+          <t>14:14:55</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>00:42:59</t>
+          <t>17:24:54</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>22:59:49</t>
+          <t>16:20:34</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>23:23:33</t>
+          <t>20:12:27</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -5139,25 +5139,25 @@
         </is>
       </c>
       <c r="M25" s="5" t="n">
-        <v>63.20000000000005</v>
+        <v>125.6500000000001</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>14.82892455320712</v>
+        <v>136.7168885797278</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>39.97585</v>
+        <v>189.99105</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>57.87321624947242</v>
+        <v>50.21471932710446</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>15.14287648205564</v>
+        <v>137.9082545861779</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>23.74308333333333</v>
+        <v>231.8833333333333</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>38.26683233039817</v>
+        <v>40.29636713820891</v>
       </c>
       <c r="T25" s="5" t="n">
         <v>0</v>
@@ -5178,121 +5178,121 @@
         <v>0</v>
       </c>
       <c r="Z25" s="5" t="n">
-        <v>25.86666666666667</v>
+        <v>23.84703333333334</v>
       </c>
       <c r="AA25" s="5" t="n">
-        <v>0</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="AB25" s="5" t="n">
-        <v>1.219860917316257</v>
+        <v>0.1926372453796382</v>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>0</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="AD25" s="5" t="n">
-        <v>2.829574292743894</v>
+        <v>0.4846822898772156</v>
       </c>
       <c r="AE25" s="5" t="n">
-        <v>0</v>
+        <v>0.2959919551202828</v>
       </c>
       <c r="AF25" s="5" t="n">
-        <v>0</v>
+        <v>3.683333333333333</v>
       </c>
       <c r="AG25" s="5" t="n">
-        <v>0</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="AH25" s="5" t="n">
-        <v>0</v>
+        <v>0.5589577464659954</v>
       </c>
       <c r="AI25" s="5" t="n">
-        <v>0</v>
+        <v>0.9627022390663391</v>
       </c>
       <c r="AJ25" s="5" t="n">
-        <v>0</v>
+        <v>9.105194060079564</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>0</v>
+        <v>13.02905285954444</v>
       </c>
       <c r="AL25" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AM25" s="5" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN25" s="5" t="n">
-        <v>0</v>
+        <v>0.1091649650425091</v>
       </c>
       <c r="AO25" s="5" t="n">
-        <v>0</v>
+        <v>0.7821753879669284</v>
       </c>
       <c r="AP25" s="5" t="n">
-        <v>0</v>
+        <v>26.19959161020218</v>
       </c>
       <c r="AQ25" s="5" t="n">
-        <v>0</v>
+        <v>4.914190919163948</v>
       </c>
       <c r="AR25" s="5" t="n">
-        <v>2.616666666666667</v>
+        <v>50.55</v>
       </c>
       <c r="AS25" s="5" t="n">
-        <v>4.02745</v>
+        <v>50.65</v>
       </c>
       <c r="AT25" s="5" t="n">
-        <v>2.15122666286036</v>
+        <v>41.38421268521648</v>
       </c>
       <c r="AU25" s="5" t="n">
-        <v>3.237008300255083</v>
+        <v>36.71220944491618</v>
       </c>
       <c r="AV25" s="5" t="n">
-        <v>49.32749035858149</v>
+        <v>49.12072722280888</v>
       </c>
       <c r="AW25" s="5" t="n">
-        <v>48.22418602721449</v>
+        <v>43.4892905566628</v>
       </c>
       <c r="AX25" s="5" t="n">
-        <v>2.816666666666667</v>
+        <v>32.7</v>
       </c>
       <c r="AY25" s="5" t="n">
-        <v>4.183333333333334</v>
+        <v>34.23333333333333</v>
       </c>
       <c r="AZ25" s="5" t="n">
-        <v>2.457618245090195</v>
+        <v>26.98832105344299</v>
       </c>
       <c r="BA25" s="5" t="n">
-        <v>2.895199368072901</v>
+        <v>25.04052735423578</v>
       </c>
       <c r="BB25" s="5" t="n">
-        <v>52.35163125635918</v>
+        <v>49.51985514393209</v>
       </c>
       <c r="BC25" s="5" t="n">
-        <v>41.52477181299778</v>
+        <v>43.8879739412117</v>
       </c>
       <c r="BD25" s="5" t="n">
-        <v>8.675850000000001</v>
+        <v>78.96068333333332</v>
       </c>
       <c r="BE25" s="5" t="n">
-        <v>15.5323</v>
+        <v>109.3</v>
       </c>
       <c r="BF25" s="5" t="n">
-        <v>9.000218727940311</v>
+        <v>67.48359488418018</v>
       </c>
       <c r="BG25" s="5" t="n">
-        <v>9.010668813727651</v>
+        <v>74.29364111773266</v>
       </c>
       <c r="BH25" s="5" t="n">
-        <v>62.24325266993074</v>
+        <v>51.27888364336781</v>
       </c>
       <c r="BI25" s="5" t="n">
-        <v>34.80747402661931</v>
+        <v>40.78333455685233</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>PAIR_028</t>
+          <t>PAIR_026</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -5302,42 +5302,42 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Maduravoyal ↔ Silk Board</t>
+          <t>Chennai ↔ Pondicherry</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Silk Board → Maduravoyal</t>
+          <t>Pondicherry → Chennai</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>18-07-2026</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>06-09-2026</t>
+          <t>26-09-2026</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>02:02:59</t>
+          <t>14:14:38</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>02:23:15</t>
+          <t>18:55:44</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>01:04:39</t>
+          <t>16:16:08</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>01:24:29</t>
+          <t>21:07:53</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -5346,160 +5346,160 @@
         </is>
       </c>
       <c r="M26" s="7" t="n">
-        <v>58.33333333333333</v>
+        <v>121.5</v>
       </c>
       <c r="N26" s="7" t="n">
-        <v>22.49736924506911</v>
+        <v>153.3729275658394</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>20.26271666666667</v>
+        <v>281.0869</v>
       </c>
       <c r="P26" s="7" t="n">
-        <v>71.17338391598146</v>
+        <v>38.12896580160068</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>22.45363674285612</v>
+        <v>154.0634351764531</v>
       </c>
       <c r="R26" s="7" t="n">
-        <v>19.8356</v>
+        <v>291.75</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>67.91920610273282</v>
+        <v>35.98974180825657</v>
       </c>
       <c r="T26" s="7" t="n">
-        <v>1.383333333333333</v>
+        <v>0</v>
       </c>
       <c r="U26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="7" t="n">
-        <v>0.1022092770638549</v>
+        <v>0</v>
       </c>
       <c r="W26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="X26" s="7" t="n">
-        <v>4.433173463010574</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z26" s="7" t="n">
-        <v>0</v>
+        <v>32.85</v>
       </c>
       <c r="AA26" s="7" t="n">
-        <v>0</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AB26" s="7" t="n">
-        <v>0</v>
+        <v>0.5585488688475958</v>
       </c>
       <c r="AC26" s="7" t="n">
-        <v>0</v>
+        <v>0.3414581795449143</v>
       </c>
       <c r="AD26" s="7" t="n">
-        <v>0</v>
+        <v>1.020180582370038</v>
       </c>
       <c r="AE26" s="7" t="n">
-        <v>0</v>
+        <v>0.7780059787099315</v>
       </c>
       <c r="AF26" s="7" t="n">
-        <v>0</v>
+        <v>9.886899999999999</v>
       </c>
       <c r="AG26" s="7" t="n">
-        <v>0</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="AH26" s="7" t="n">
-        <v>0</v>
+        <v>1.34706205013313</v>
       </c>
       <c r="AI26" s="7" t="n">
-        <v>0</v>
+        <v>0.5256426997626461</v>
       </c>
       <c r="AJ26" s="7" t="n">
-        <v>0</v>
+        <v>8.174829623844461</v>
       </c>
       <c r="AK26" s="7" t="n">
-        <v>0</v>
+        <v>3.148608517713021</v>
       </c>
       <c r="AL26" s="7" t="n">
-        <v>0</v>
+        <v>7.933333333333334</v>
       </c>
       <c r="AM26" s="7" t="n">
-        <v>0.08333333333333333</v>
+        <v>14.48333333333333</v>
       </c>
       <c r="AN26" s="7" t="n">
-        <v>0</v>
+        <v>1.158895058334316</v>
       </c>
       <c r="AO26" s="7" t="n">
-        <v>0.005475177103936694</v>
+        <v>1.222282616060936</v>
       </c>
       <c r="AP26" s="7" t="n">
-        <v>0</v>
+        <v>8.764752542024238</v>
       </c>
       <c r="AQ26" s="7" t="n">
-        <v>3.94212751483442</v>
+        <v>5.063541332358309</v>
       </c>
       <c r="AR26" s="7" t="n">
-        <v>3.639233333333334</v>
+        <v>61.06666666666667</v>
       </c>
       <c r="AS26" s="7" t="n">
-        <v>4.933333333333334</v>
+        <v>52.6</v>
       </c>
       <c r="AT26" s="7" t="n">
-        <v>3.966520593106893</v>
+        <v>45.26405758465819</v>
       </c>
       <c r="AU26" s="7" t="n">
-        <v>4.72826041501822</v>
+        <v>30.18268163700424</v>
       </c>
       <c r="AV26" s="7" t="n">
-        <v>65.39598145756347</v>
+        <v>44.47341902422747</v>
       </c>
       <c r="AW26" s="7" t="n">
-        <v>57.50586991238376</v>
+        <v>34.42891441483373</v>
       </c>
       <c r="AX26" s="7" t="n">
-        <v>3.5</v>
+        <v>46.8</v>
       </c>
       <c r="AY26" s="7" t="n">
-        <v>2.966666666666667</v>
+        <v>42.23333333333333</v>
       </c>
       <c r="AZ26" s="7" t="n">
-        <v>3.418758869278361</v>
+        <v>33.58518042089994</v>
       </c>
       <c r="BA26" s="7" t="n">
-        <v>3.094319836595824</v>
+        <v>24.88861936987865</v>
       </c>
       <c r="BB26" s="7" t="n">
-        <v>58.60729490191476</v>
+        <v>43.05792361653838</v>
       </c>
       <c r="BC26" s="7" t="n">
-        <v>62.58174950418521</v>
+        <v>35.35873312216383</v>
       </c>
       <c r="BD26" s="7" t="n">
-        <v>11.74015</v>
+        <v>122.55</v>
       </c>
       <c r="BE26" s="7" t="n">
-        <v>11.85226666666667</v>
+        <v>146.0833333333333</v>
       </c>
       <c r="BF26" s="7" t="n">
-        <v>15.00988050562</v>
+        <v>71.45918358296625</v>
       </c>
       <c r="BG26" s="7" t="n">
-        <v>14.62558131413813</v>
+        <v>96.90275067420166</v>
       </c>
       <c r="BH26" s="7" t="n">
-        <v>76.71050457934524</v>
+        <v>34.98613639312913</v>
       </c>
       <c r="BI26" s="7" t="n">
-        <v>74.03941402333344</v>
+        <v>39.80033113829162</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>PAIR_029</t>
+          <t>PAIR_027</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -5524,27 +5524,27 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>18-07-2026</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>15:48:40</t>
+          <t>14:31:24</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>16:31:32</t>
+          <t>18:11:19</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>17:49:35</t>
+          <t>16:20:34</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>18:35:05</t>
+          <t>20:12:27</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -5553,25 +5553,25 @@
         </is>
       </c>
       <c r="M27" s="5" t="n">
-        <v>120.9166666666666</v>
+        <v>109.1666666666667</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>34.43958194459641</v>
+        <v>138.2944646000696</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>42.85905</v>
+        <v>219.9088</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>49.88240215190034</v>
+        <v>46.48372876031184</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>34.32677600023323</v>
+        <v>137.8693466671948</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>45.4903</v>
+        <v>231.8833333333333</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>45.25609711599014</v>
+        <v>40.28662307790311</v>
       </c>
       <c r="T27" s="5" t="n">
         <v>0</v>
@@ -5592,121 +5592,121 @@
         <v>0</v>
       </c>
       <c r="Z27" s="5" t="n">
-        <v>0</v>
+        <v>31.03333333333333</v>
       </c>
       <c r="AA27" s="5" t="n">
-        <v>0</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="AB27" s="5" t="n">
-        <v>0</v>
+        <v>0.1769495542483206</v>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>0</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="AD27" s="5" t="n">
-        <v>0</v>
+        <v>0.342115142477956</v>
       </c>
       <c r="AE27" s="5" t="n">
-        <v>0</v>
+        <v>0.2959919551202828</v>
       </c>
       <c r="AF27" s="5" t="n">
-        <v>1.5</v>
+        <v>10.96666666666667</v>
       </c>
       <c r="AG27" s="5" t="n">
-        <v>0.1666666666666667</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="AH27" s="5" t="n">
-        <v>0.05476919925384444</v>
+        <v>0.2864416579452221</v>
       </c>
       <c r="AI27" s="5" t="n">
-        <v>0.1405968038522134</v>
+        <v>0.9568808181881884</v>
       </c>
       <c r="AJ27" s="5" t="n">
-        <v>2.190767970153778</v>
+        <v>1.567158006995135</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>50.61484938679681</v>
+        <v>12.95026671232135</v>
       </c>
       <c r="AL27" s="5" t="n">
-        <v>0.1666666666666667</v>
+        <v>2.933333333333333</v>
       </c>
       <c r="AM27" s="5" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN27" s="5" t="n">
-        <v>0.01267380267082223</v>
+        <v>0.2376855524103972</v>
       </c>
       <c r="AO27" s="5" t="n">
-        <v>0</v>
+        <v>0.7490888898619357</v>
       </c>
       <c r="AP27" s="5" t="n">
-        <v>4.562568961496002</v>
+        <v>4.861749935667216</v>
       </c>
       <c r="AQ27" s="5" t="n">
-        <v>0</v>
+        <v>4.706317632640434</v>
       </c>
       <c r="AR27" s="5" t="n">
-        <v>15.90041666666667</v>
+        <v>62.68333333333333</v>
       </c>
       <c r="AS27" s="5" t="n">
-        <v>10.95</v>
+        <v>50.65</v>
       </c>
       <c r="AT27" s="5" t="n">
-        <v>13.25093473030296</v>
+        <v>48.51346678639188</v>
       </c>
       <c r="AU27" s="5" t="n">
-        <v>8.219513195924231</v>
+        <v>36.71220944491618</v>
       </c>
       <c r="AV27" s="5" t="n">
-        <v>50.00221695352915</v>
+        <v>46.43671375458941</v>
       </c>
       <c r="AW27" s="5" t="n">
-        <v>45.03842847081771</v>
+        <v>43.4892905566628</v>
       </c>
       <c r="AX27" s="5" t="n">
-        <v>12.59196666666667</v>
+        <v>46.94098333333333</v>
       </c>
       <c r="AY27" s="5" t="n">
-        <v>8.85</v>
+        <v>34.23333333333333</v>
       </c>
       <c r="AZ27" s="5" t="n">
-        <v>9.785494672181397</v>
+        <v>34.6641680603018</v>
       </c>
       <c r="BA27" s="5" t="n">
-        <v>6.487184809227589</v>
+        <v>25.04052735423578</v>
       </c>
       <c r="BB27" s="5" t="n">
-        <v>46.62732167844184</v>
+        <v>44.30776553718214</v>
       </c>
       <c r="BC27" s="5" t="n">
-        <v>43.98091396086501</v>
+        <v>43.8879739412117</v>
       </c>
       <c r="BD27" s="5" t="n">
-        <v>12.7</v>
+        <v>65.35115</v>
       </c>
       <c r="BE27" s="5" t="n">
-        <v>25.52363333333333</v>
+        <v>109.3</v>
       </c>
       <c r="BF27" s="5" t="n">
-        <v>11.33570954018739</v>
+        <v>54.41575298877198</v>
       </c>
       <c r="BG27" s="5" t="n">
-        <v>19.4794811912292</v>
+        <v>74.29364111773266</v>
       </c>
       <c r="BH27" s="5" t="n">
-        <v>53.55453326072782</v>
+        <v>49.96002640085627</v>
       </c>
       <c r="BI27" s="5" t="n">
-        <v>45.79163382461558</v>
+        <v>40.78333455685233</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>PAIR_030</t>
+          <t>PAIR_029</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -5716,42 +5716,42 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Maduravoyal ↔ Silk Board</t>
+          <t>Chennai ↔ Pondicherry</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Silk Board → Maduravoyal</t>
+          <t>Chennai → Pondicherry</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>06-09-2026</t>
+          <t>19-07-2026</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>29-07-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>00:48:04</t>
+          <t>09:10:36</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>04:39:51</t>
+          <t>12:33:03</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>23:36:23</t>
+          <t>14:45:59</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>03:10:17</t>
+          <t>19:12:44</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -5760,160 +5760,160 @@
         </is>
       </c>
       <c r="M28" s="7" t="n">
-        <v>71.68333333333317</v>
+        <v>335.3833333333333</v>
       </c>
       <c r="N28" s="7" t="n">
-        <v>231.4242273523428</v>
+        <v>148.6184563331109</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>231.7772166666667</v>
+        <v>202.4542833333333</v>
       </c>
       <c r="P28" s="7" t="n">
-        <v>67.59910743007244</v>
+        <v>47.68589618099658</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>231.3323956071126</v>
+        <v>148.5522231625584</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>213.89885</v>
+        <v>266.7375833333334</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>70.84744357406082</v>
+        <v>42.94452978486028</v>
       </c>
       <c r="T28" s="7" t="n">
-        <v>21.51666666666667</v>
+        <v>0</v>
       </c>
       <c r="U28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="7" t="n">
-        <v>0.814768997799896</v>
+        <v>0</v>
       </c>
       <c r="W28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="X28" s="7" t="n">
-        <v>2.272012697195682</v>
+        <v>0</v>
       </c>
       <c r="Y28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z28" s="7" t="n">
-        <v>3.666666666666667</v>
+        <v>12.03333333333333</v>
       </c>
       <c r="AA28" s="7" t="n">
-        <v>18.1</v>
+        <v>48.18333333333333</v>
       </c>
       <c r="AB28" s="7" t="n">
-        <v>0.1409484311311202</v>
+        <v>0.3736603870816042</v>
       </c>
       <c r="AC28" s="7" t="n">
-        <v>0.2136487015115684</v>
+        <v>0.6526929809004927</v>
       </c>
       <c r="AD28" s="7" t="n">
-        <v>2.306428873054694</v>
+        <v>1.863126583786393</v>
       </c>
       <c r="AE28" s="7" t="n">
-        <v>0.7082277398173538</v>
+        <v>0.8127619270985035</v>
       </c>
       <c r="AF28" s="7" t="n">
-        <v>2.033333333333333</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="AG28" s="7" t="n">
-        <v>0.06666666666666667</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="AH28" s="7" t="n">
-        <v>0</v>
+        <v>0.8124960099708274</v>
       </c>
       <c r="AI28" s="7" t="n">
-        <v>0</v>
+        <v>1.252848098218356</v>
       </c>
       <c r="AJ28" s="7" t="n">
-        <v>0</v>
+        <v>9.915205545406705</v>
       </c>
       <c r="AK28" s="7" t="n">
-        <v>0</v>
+        <v>5.500308723885465</v>
       </c>
       <c r="AL28" s="7" t="n">
-        <v>4.71055</v>
+        <v>0</v>
       </c>
       <c r="AM28" s="7" t="n">
-        <v>1.416666666666667</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AN28" s="7" t="n">
-        <v>0.5708869176953876</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="7" t="n">
-        <v>0.2061655756673897</v>
+        <v>1.149895932972568</v>
       </c>
       <c r="AP28" s="7" t="n">
-        <v>7.271595686644502</v>
+        <v>0</v>
       </c>
       <c r="AQ28" s="7" t="n">
-        <v>8.73171849885415</v>
+        <v>8.069445143667142</v>
       </c>
       <c r="AR28" s="7" t="n">
-        <v>26.75</v>
+        <v>47.07095</v>
       </c>
       <c r="AS28" s="7" t="n">
-        <v>36.55</v>
+        <v>47.50425</v>
       </c>
       <c r="AT28" s="7" t="n">
-        <v>25.92939460092482</v>
+        <v>37.76245819389838</v>
       </c>
       <c r="AU28" s="7" t="n">
-        <v>38.59680733466195</v>
+        <v>30.80621122533811</v>
       </c>
       <c r="AV28" s="7" t="n">
-        <v>58.15938975908371</v>
+        <v>48.13473047886016</v>
       </c>
       <c r="AW28" s="7" t="n">
-        <v>63.36001204048475</v>
+        <v>38.90962752849033</v>
       </c>
       <c r="AX28" s="7" t="n">
-        <v>24.85</v>
+        <v>35.88333333333333</v>
       </c>
       <c r="AY28" s="7" t="n">
-        <v>25.63333333333333</v>
+        <v>34.78333333333333</v>
       </c>
       <c r="AZ28" s="7" t="n">
-        <v>25.11723460299349</v>
+        <v>27.85743429121439</v>
       </c>
       <c r="BA28" s="7" t="n">
-        <v>26.87122394746974</v>
+        <v>23.37216669639708</v>
       </c>
       <c r="BB28" s="7" t="n">
-        <v>60.64523445390783</v>
+        <v>46.58001089102267</v>
       </c>
       <c r="BC28" s="7" t="n">
-        <v>62.89753329706833</v>
+        <v>40.31614763154264</v>
       </c>
       <c r="BD28" s="7" t="n">
-        <v>148.25</v>
+        <v>102.55</v>
       </c>
       <c r="BE28" s="7" t="n">
-        <v>132.1321833333333</v>
+        <v>114.05</v>
       </c>
       <c r="BF28" s="7" t="n">
-        <v>178.8509938017981</v>
+        <v>81.8124074509457</v>
       </c>
       <c r="BG28" s="7" t="n">
-        <v>165.4445500478019</v>
+        <v>91.31840822873183</v>
       </c>
       <c r="BH28" s="7" t="n">
-        <v>72.38488787931121</v>
+        <v>47.86684004931002</v>
       </c>
       <c r="BI28" s="7" t="n">
-        <v>75.12683702369344</v>
+        <v>48.04124939696545</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>PAIR_031</t>
+          <t>PAIR_030</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -5923,42 +5923,42 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Maduravoyal ↔ Silk Board</t>
+          <t>Chennai ↔ Pondicherry</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Maduravoyal → Silk Board</t>
+          <t>Chennai → Pondicherry</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>19-07-2026</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>01:04:25</t>
+          <t>13:56:09</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>01:19:18</t>
+          <t>18:11:54</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>00:13:45</t>
+          <t>11:08:45</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>00:30:31</t>
+          <t>15:34:22</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -5967,25 +5967,25 @@
         </is>
       </c>
       <c r="M29" s="5" t="n">
-        <v>50.66666666666667</v>
+        <v>167.4</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>12.73848083938423</v>
+        <v>145.9773325040056</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>14.8788</v>
+        <v>255.7438833333333</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>51.36898475435208</v>
+        <v>47.2452299004206</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>12.6496249595659</v>
+        <v>145.8893363990339</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>16.75645</v>
+        <v>265.6299833333333</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>45.29464758788131</v>
+        <v>45.59497163487288</v>
       </c>
       <c r="T29" s="5" t="n">
         <v>0</v>
@@ -6006,121 +6006,121 @@
         <v>0</v>
       </c>
       <c r="Z29" s="5" t="n">
-        <v>0</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="AA29" s="5" t="n">
-        <v>0</v>
+        <v>71.08333333333333</v>
       </c>
       <c r="AB29" s="5" t="n">
-        <v>0</v>
+        <v>0.6992727007011277</v>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>0</v>
+        <v>0.5752841088710083</v>
       </c>
       <c r="AD29" s="5" t="n">
-        <v>0</v>
+        <v>0.9289231448428267</v>
       </c>
       <c r="AE29" s="5" t="n">
-        <v>0</v>
+        <v>0.4855856487539578</v>
       </c>
       <c r="AF29" s="5" t="n">
-        <v>0</v>
+        <v>26.67068333333333</v>
       </c>
       <c r="AG29" s="5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AH29" s="5" t="n">
-        <v>0</v>
+        <v>0.4662856779261432</v>
       </c>
       <c r="AI29" s="5" t="n">
-        <v>0</v>
+        <v>0.5525630686911562</v>
       </c>
       <c r="AJ29" s="5" t="n">
-        <v>0</v>
+        <v>1.04898477200254</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>0</v>
+        <v>8.186119536165277</v>
       </c>
       <c r="AL29" s="5" t="n">
-        <v>0</v>
+        <v>2.883333333333333</v>
       </c>
       <c r="AM29" s="5" t="n">
-        <v>0.08333333333333333</v>
+        <v>7.683333333333334</v>
       </c>
       <c r="AN29" s="5" t="n">
-        <v>0</v>
+        <v>0.2514853038814903</v>
       </c>
       <c r="AO29" s="5" t="n">
-        <v>0.01248000402488661</v>
+        <v>0.6833899734934139</v>
       </c>
       <c r="AP29" s="5" t="n">
-        <v>0</v>
+        <v>5.233220196377834</v>
       </c>
       <c r="AQ29" s="5" t="n">
-        <v>8.985602897918358</v>
+        <v>5.336667905805401</v>
       </c>
       <c r="AR29" s="5" t="n">
-        <v>2.1</v>
+        <v>61.42319999999999</v>
       </c>
       <c r="AS29" s="5" t="n">
-        <v>3.266666666666667</v>
+        <v>38.68333333333333</v>
       </c>
       <c r="AT29" s="5" t="n">
-        <v>1.57280616355066</v>
+        <v>44.94924920648065</v>
       </c>
       <c r="AU29" s="5" t="n">
-        <v>2.59336123238131</v>
+        <v>27.60990969505806</v>
       </c>
       <c r="AV29" s="5" t="n">
-        <v>44.93731895859029</v>
+        <v>43.90775720556466</v>
       </c>
       <c r="AW29" s="5" t="n">
-        <v>47.63316549271794</v>
+        <v>42.82450448177899</v>
       </c>
       <c r="AX29" s="5" t="n">
-        <v>2.43445</v>
+        <v>44.01666666666667</v>
       </c>
       <c r="AY29" s="5" t="n">
-        <v>2.623083333333333</v>
+        <v>26.81666666666667</v>
       </c>
       <c r="AZ29" s="5" t="n">
-        <v>1.851109043655713</v>
+        <v>32.63164533881391</v>
       </c>
       <c r="BA29" s="5" t="n">
-        <v>1.975517359737947</v>
+        <v>19.89292827190748</v>
       </c>
       <c r="BB29" s="5" t="n">
-        <v>45.62284812559008</v>
+        <v>44.48084938270733</v>
       </c>
       <c r="BC29" s="5" t="n">
-        <v>45.18767668492302</v>
+        <v>44.50872702229143</v>
       </c>
       <c r="BD29" s="5" t="n">
-        <v>10.34435</v>
+        <v>75.58333333333333</v>
       </c>
       <c r="BE29" s="5" t="n">
-        <v>10.78336666666667</v>
+        <v>117.3133166666667</v>
       </c>
       <c r="BF29" s="5" t="n">
-        <v>9.314565632177855</v>
+        <v>66.97939427620221</v>
       </c>
       <c r="BG29" s="5" t="n">
-        <v>8.068266363421753</v>
+        <v>96.5752612810128</v>
       </c>
       <c r="BH29" s="5" t="n">
-        <v>54.02697491197333</v>
+        <v>53.16997120051334</v>
       </c>
       <c r="BI29" s="5" t="n">
-        <v>44.89284253884579</v>
+        <v>49.39350315467823</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>PAIR_034</t>
+          <t>PAIR_032</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -6130,42 +6130,42 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Madhuravoyal to Madiwala</t>
+          <t>Maduravoyal ↔ Silk Board</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Madhuravoyal to Madiwala</t>
+          <t>Silk Board → Maduravoyal</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>20-07-2026</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>29-07-2026</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>23:19:37</t>
+          <t>00:01:12</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>00:25:38</t>
+          <t>05:57:20</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>17:17:37</t>
+          <t>22:58:13</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>18:51:46</t>
+          <t>04:31:39</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
@@ -6174,160 +6174,160 @@
         </is>
       </c>
       <c r="M30" s="7" t="n">
-        <v>362</v>
+        <v>62.98333333333335</v>
       </c>
       <c r="N30" s="7" t="n">
-        <v>49.09342708546251</v>
+        <v>324.8278468558257</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>66.01939999999999</v>
+        <v>356.1224666666666</v>
       </c>
       <c r="P30" s="7" t="n">
-        <v>47.58550177729312</v>
+        <v>65.68858194612334</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>49.01363547616007</v>
+        <v>330.6538536572841</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>94.14933333333333</v>
+        <v>333.4333333333333</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>37.18511343393678</v>
+        <v>62.88775311063549</v>
       </c>
       <c r="T30" s="7" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="U30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="7" t="n">
-        <v>0</v>
+        <v>0.1419108710453242</v>
       </c>
       <c r="W30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="X30" s="7" t="n">
-        <v>0</v>
+        <v>0.3638740283213441</v>
       </c>
       <c r="Y30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z30" s="7" t="n">
-        <v>3.95</v>
+        <v>37.61666666666667</v>
       </c>
       <c r="AA30" s="7" t="n">
-        <v>14.7</v>
+        <v>18.1</v>
       </c>
       <c r="AB30" s="7" t="n">
-        <v>0.06497427594259966</v>
+        <v>1.601243883509142</v>
       </c>
       <c r="AC30" s="7" t="n">
-        <v>0.3781894421708778</v>
+        <v>0.2136487015115684</v>
       </c>
       <c r="AD30" s="7" t="n">
-        <v>0.9869510269761974</v>
+        <v>2.554044298020785</v>
       </c>
       <c r="AE30" s="7" t="n">
-        <v>1.543630376207665</v>
+        <v>0.7082277398173538</v>
       </c>
       <c r="AF30" s="7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AG30" s="7" t="n">
-        <v>1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="AH30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AI30" s="7" t="n">
-        <v>0.01632338704389566</v>
+        <v>0</v>
       </c>
       <c r="AJ30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AK30" s="7" t="n">
-        <v>0.9794032226337396</v>
+        <v>0</v>
       </c>
       <c r="AL30" s="7" t="n">
-        <v>1</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AM30" s="7" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AN30" s="7" t="n">
-        <v>0.07825898700519315</v>
+        <v>0.2289474824354939</v>
       </c>
       <c r="AO30" s="7" t="n">
-        <v>0.1903594564923157</v>
+        <v>0.3073128194596925</v>
       </c>
       <c r="AP30" s="7" t="n">
-        <v>4.69553922031159</v>
+        <v>23.5488839076508</v>
       </c>
       <c r="AQ30" s="7" t="n">
-        <v>6.922162054266026</v>
+        <v>10.53643952433232</v>
       </c>
       <c r="AR30" s="7" t="n">
-        <v>21.19846666666666</v>
+        <v>58.38913333333333</v>
       </c>
       <c r="AS30" s="7" t="n">
-        <v>24.53266666666667</v>
+        <v>61.95</v>
       </c>
       <c r="AT30" s="7" t="n">
-        <v>17.20758212650452</v>
+        <v>60.39000878394881</v>
       </c>
       <c r="AU30" s="7" t="n">
-        <v>16.02491169354092</v>
+        <v>59.1588856042147</v>
       </c>
       <c r="AV30" s="7" t="n">
-        <v>48.70422676436997</v>
+        <v>62.05607653656323</v>
       </c>
       <c r="AW30" s="7" t="n">
-        <v>39.19242513162538</v>
+        <v>57.29674150529269</v>
       </c>
       <c r="AX30" s="7" t="n">
-        <v>15.75426666666667</v>
+        <v>47.78333333333333</v>
       </c>
       <c r="AY30" s="7" t="n">
-        <v>17.41666666666667</v>
+        <v>44.95</v>
       </c>
       <c r="AZ30" s="7" t="n">
-        <v>12.63780002856964</v>
+        <v>48.61834668820352</v>
       </c>
       <c r="BA30" s="7" t="n">
-        <v>11.032089516834</v>
+        <v>41.61929530648353</v>
       </c>
       <c r="BB30" s="7" t="n">
-        <v>48.13096145684417</v>
+        <v>61.04849950384817</v>
       </c>
       <c r="BC30" s="7" t="n">
-        <v>38.00528445990659</v>
+        <v>55.5541205425809</v>
       </c>
       <c r="BD30" s="7" t="n">
-        <v>23.86666666666667</v>
+        <v>188.35</v>
       </c>
       <c r="BE30" s="7" t="n">
-        <v>34.85</v>
+        <v>206.6166666666667</v>
       </c>
       <c r="BF30" s="7" t="n">
-        <v>19.10481166744055</v>
+        <v>213.8473891466835</v>
       </c>
       <c r="BG30" s="7" t="n">
-        <v>21.37176198007807</v>
+        <v>229.3547112256146</v>
       </c>
       <c r="BH30" s="7" t="n">
-        <v>48.02885614719691</v>
+        <v>68.12234323759496</v>
       </c>
       <c r="BI30" s="7" t="n">
-        <v>36.79499910486898</v>
+        <v>66.60296526677523</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>PAIR_036</t>
+          <t>PAIR_033</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -6337,42 +6337,42 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Madiwala to Madhuravoyal</t>
+          <t>Maduravoyal ↔ Silk Board</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Madiwala to Madhuravoyal</t>
+          <t>Silk Board → Maduravoyal</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>13-09-2026</t>
+          <t>20-07-2026</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>20-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>02:49:31</t>
+          <t>00:02:48</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>03:01:14</t>
+          <t>05:52:52</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>14:32:06</t>
+          <t>23:17:40</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>14:43:49</t>
+          <t>04:34:59</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -6381,160 +6381,160 @@
         </is>
       </c>
       <c r="M31" s="5" t="n">
-        <v>702.5833333333334</v>
+        <v>45.13333333333321</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>16.43424965629278</v>
+        <v>320.295003456412</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>11.71183333333333</v>
+        <v>350.0545666666667</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>84.19305084978724</v>
+        <v>66.1266599366777</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>16.43868693033036</v>
+        <v>320.9302329433269</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>11.73173333333333</v>
+        <v>317.3162</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>84.07293174806406</v>
+        <v>65.88396841768795</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="U31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V31" s="5" t="n">
-        <v>0</v>
+        <v>0.1419108710453242</v>
       </c>
       <c r="W31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X31" s="5" t="n">
-        <v>0</v>
+        <v>0.3638740283213441</v>
       </c>
       <c r="Y31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Z31" s="5" t="n">
-        <v>0</v>
+        <v>37.61666666666667</v>
       </c>
       <c r="AA31" s="5" t="n">
-        <v>0</v>
+        <v>16.43333333333333</v>
       </c>
       <c r="AB31" s="5" t="n">
-        <v>0</v>
+        <v>1.601243883509142</v>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>0</v>
+        <v>0.08388219724002884</v>
       </c>
       <c r="AD31" s="5" t="n">
-        <v>0</v>
+        <v>2.554044298020785</v>
       </c>
       <c r="AE31" s="5" t="n">
-        <v>0</v>
+        <v>0.3062636004706936</v>
       </c>
       <c r="AF31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AG31" s="5" t="n">
-        <v>0</v>
+        <v>8.733333333333333</v>
       </c>
       <c r="AH31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI31" s="5" t="n">
-        <v>0</v>
+        <v>0.0468402898266811</v>
       </c>
       <c r="AJ31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>0</v>
+        <v>0.3218035178932289</v>
       </c>
       <c r="AL31" s="5" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AM31" s="5" t="n">
-        <v>0</v>
+        <v>5.083333333333333</v>
       </c>
       <c r="AN31" s="5" t="n">
-        <v>0</v>
+        <v>0.2289474824354939</v>
       </c>
       <c r="AO31" s="5" t="n">
-        <v>0</v>
+        <v>0.2495284473497653</v>
       </c>
       <c r="AP31" s="5" t="n">
-        <v>0</v>
+        <v>23.5488839076508</v>
       </c>
       <c r="AQ31" s="5" t="n">
-        <v>0</v>
+        <v>2.945253804784115</v>
       </c>
       <c r="AR31" s="5" t="n">
-        <v>1.5</v>
+        <v>56.67031666666666</v>
       </c>
       <c r="AS31" s="5" t="n">
-        <v>1.683333333333333</v>
+        <v>63.81666666666667</v>
       </c>
       <c r="AT31" s="5" t="n">
-        <v>2.145589159808596</v>
+        <v>59.19131521643719</v>
       </c>
       <c r="AU31" s="5" t="n">
-        <v>2.354103498469736</v>
+        <v>61.45979625723403</v>
       </c>
       <c r="AV31" s="5" t="n">
-        <v>85.82356639234384</v>
+        <v>62.6691206593381</v>
       </c>
       <c r="AW31" s="5" t="n">
-        <v>83.90863954941635</v>
+        <v>57.78408632176613</v>
       </c>
       <c r="AX31" s="5" t="n">
-        <v>1.233333333333333</v>
+        <v>46.80091666666667</v>
       </c>
       <c r="AY31" s="5" t="n">
-        <v>2.23205</v>
+        <v>46.86666666666667</v>
       </c>
       <c r="AZ31" s="5" t="n">
-        <v>1.726998909362367</v>
+        <v>47.93000682714188</v>
       </c>
       <c r="BA31" s="5" t="n">
-        <v>2.895877582706585</v>
+        <v>46.93257746538925</v>
       </c>
       <c r="BB31" s="5" t="n">
-        <v>84.01616315816923</v>
+        <v>61.44752313530567</v>
       </c>
       <c r="BC31" s="5" t="n">
-        <v>77.84442775134745</v>
+        <v>60.08438082340018</v>
       </c>
       <c r="BD31" s="5" t="n">
-        <v>8.9785</v>
+        <v>184.9833333333333</v>
       </c>
       <c r="BE31" s="5" t="n">
-        <v>7.81635</v>
+        <v>176.3828666666667</v>
       </c>
       <c r="BF31" s="5" t="n">
-        <v>12.56166158712181</v>
+        <v>211.201579175843</v>
       </c>
       <c r="BG31" s="5" t="n">
-        <v>11.18870584915403</v>
+        <v>212.1576082862871</v>
       </c>
       <c r="BH31" s="5" t="n">
-        <v>83.94494572894232</v>
+        <v>68.5039809922547</v>
       </c>
       <c r="BI31" s="5" t="n">
-        <v>85.88693583952124</v>
+        <v>72.16946145474384</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>PAIR_037</t>
+          <t>PAIR_034</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -6544,199 +6544,2683 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
+          <t>Chennai ↔ Pondicherry</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Pondicherry → Chennai</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>20-07-2026</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>26-09-2026</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>14:14:55</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>18:27:46</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>16:16:08</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>21:07:53</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>121.2166666666667</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>152.3946794802466</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>252.8470333333333</v>
+      </c>
+      <c r="P32" s="7" t="n">
+        <v>42.28793493991633</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>154.0323598514136</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <v>35.98718333260023</v>
+      </c>
+      <c r="T32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="7" t="n">
+        <v>34.49703333333333</v>
+      </c>
+      <c r="AA32" s="7" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AB32" s="7" t="n">
+        <v>0.5388878376354634</v>
+      </c>
+      <c r="AC32" s="7" t="n">
+        <v>0.321273432549297</v>
+      </c>
+      <c r="AD32" s="7" t="n">
+        <v>0.9372768361181149</v>
+      </c>
+      <c r="AE32" s="7" t="n">
+        <v>0.7320154159351072</v>
+      </c>
+      <c r="AF32" s="7" t="n">
+        <v>3.683333333333333</v>
+      </c>
+      <c r="AG32" s="7" t="n">
+        <v>10.01666666666667</v>
+      </c>
+      <c r="AH32" s="7" t="n">
+        <v>0.5589577464659954</v>
+      </c>
+      <c r="AI32" s="7" t="n">
+        <v>0.5256426997626461</v>
+      </c>
+      <c r="AJ32" s="7" t="n">
+        <v>9.105194060079564</v>
+      </c>
+      <c r="AK32" s="7" t="n">
+        <v>3.148608517713021</v>
+      </c>
+      <c r="AL32" s="7" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="AM32" s="7" t="n">
+        <v>14.48333333333333</v>
+      </c>
+      <c r="AN32" s="7" t="n">
+        <v>0.6798850900122044</v>
+      </c>
+      <c r="AO32" s="7" t="n">
+        <v>1.222282616060936</v>
+      </c>
+      <c r="AP32" s="7" t="n">
+        <v>5.550082367446567</v>
+      </c>
+      <c r="AQ32" s="7" t="n">
+        <v>5.063541332358309</v>
+      </c>
+      <c r="AR32" s="7" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="AS32" s="7" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AT32" s="7" t="n">
+        <v>44.66597796080278</v>
+      </c>
+      <c r="AU32" s="7" t="n">
+        <v>30.18268163700424</v>
+      </c>
+      <c r="AV32" s="7" t="n">
+        <v>46.56748353863018</v>
+      </c>
+      <c r="AW32" s="7" t="n">
+        <v>34.42891441483373</v>
+      </c>
+      <c r="AX32" s="7" t="n">
+        <v>37.36666666666667</v>
+      </c>
+      <c r="AY32" s="7" t="n">
+        <v>42.23333333333333</v>
+      </c>
+      <c r="AZ32" s="7" t="n">
+        <v>29.46179071078489</v>
+      </c>
+      <c r="BA32" s="7" t="n">
+        <v>24.87772879183483</v>
+      </c>
+      <c r="BB32" s="7" t="n">
+        <v>47.30706804586334</v>
+      </c>
+      <c r="BC32" s="7" t="n">
+        <v>35.34326110915762</v>
+      </c>
+      <c r="BD32" s="7" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="BE32" s="7" t="n">
+        <v>146.0833333333333</v>
+      </c>
+      <c r="BF32" s="7" t="n">
+        <v>76.48918013454522</v>
+      </c>
+      <c r="BG32" s="7" t="n">
+        <v>96.90275067420166</v>
+      </c>
+      <c r="BH32" s="7" t="n">
+        <v>40.83052320349389</v>
+      </c>
+      <c r="BI32" s="7" t="n">
+        <v>39.80033113829162</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Chennai ↔ Pondicherry</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Pondicherry → Chennai</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>26-09-2026</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>20-07-2026</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>15:19:03</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>18:34:00</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>16:56:44</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>20:11:41</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>97.68333333333339</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>125.7416693023907</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>194.9381166666667</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>45.47510257059169</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>123.9823800042885</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>194.9584</v>
+      </c>
+      <c r="S33" s="5" t="n">
+        <v>42.7689234538736</v>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="5" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="AA33" s="5" t="n">
+        <v>21.38333333333333</v>
+      </c>
+      <c r="AB33" s="5" t="n">
+        <v>0.07050792832939867</v>
+      </c>
+      <c r="AC33" s="5" t="n">
+        <v>0.1090721560237224</v>
+      </c>
+      <c r="AD33" s="5" t="n">
+        <v>0.2048656513202867</v>
+      </c>
+      <c r="AE33" s="5" t="n">
+        <v>0.3060481384921284</v>
+      </c>
+      <c r="AF33" s="5" t="n">
+        <v>8.668333333333333</v>
+      </c>
+      <c r="AG33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH33" s="5" t="n">
+        <v>0.1448841273528465</v>
+      </c>
+      <c r="AI33" s="5" t="n">
+        <v>0.8591442430348036</v>
+      </c>
+      <c r="AJ33" s="5" t="n">
+        <v>1.002851102615357</v>
+      </c>
+      <c r="AK33" s="5" t="n">
+        <v>51.54865458208822</v>
+      </c>
+      <c r="AL33" s="5" t="n">
+        <v>2.983333333333333</v>
+      </c>
+      <c r="AM33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="5" t="n">
+        <v>0.259210764002235</v>
+      </c>
+      <c r="AO33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" s="5" t="n">
+        <v>5.213177376581262</v>
+      </c>
+      <c r="AQ33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" s="5" t="n">
+        <v>56.78333333333333</v>
+      </c>
+      <c r="AS33" s="5" t="n">
+        <v>39.18333333333333</v>
+      </c>
+      <c r="AT33" s="5" t="n">
+        <v>43.79816613863036</v>
+      </c>
+      <c r="AU33" s="5" t="n">
+        <v>28.21320161975721</v>
+      </c>
+      <c r="AV33" s="5" t="n">
+        <v>46.27924804786301</v>
+      </c>
+      <c r="AW33" s="5" t="n">
+        <v>43.20183999622542</v>
+      </c>
+      <c r="AX33" s="5" t="n">
+        <v>43.36978333333333</v>
+      </c>
+      <c r="AY33" s="5" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AZ33" s="5" t="n">
+        <v>31.32770704550355</v>
+      </c>
+      <c r="BA33" s="5" t="n">
+        <v>20.93633895165053</v>
+      </c>
+      <c r="BB33" s="5" t="n">
+        <v>43.34036922166347</v>
+      </c>
+      <c r="BC33" s="5" t="n">
+        <v>41.23130209296603</v>
+      </c>
+      <c r="BD33" s="5" t="n">
+        <v>62.48333333333333</v>
+      </c>
+      <c r="BE33" s="5" t="n">
+        <v>102.9250666666667</v>
+      </c>
+      <c r="BF33" s="5" t="n">
+        <v>50.14119329857225</v>
+      </c>
+      <c r="BG33" s="5" t="n">
+        <v>73.86462303382228</v>
+      </c>
+      <c r="BH33" s="5" t="n">
+        <v>48.14838513599896</v>
+      </c>
+      <c r="BI33" s="5" t="n">
+        <v>43.05926170912692</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>PAIR_036</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Maduravoyal ↔ Silk Board</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Maduravoyal → Silk Board</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>31-07-2026</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>00:04:24</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>08:02:01</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>23:17:40</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>05:25:45</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>46.73333333333335</v>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>326.4581126643001</v>
+      </c>
+      <c r="O34" s="7" t="n">
+        <v>477.62115</v>
+      </c>
+      <c r="P34" s="7" t="n">
+        <v>53.20517022732241</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>326.5906174282528</v>
+      </c>
+      <c r="R34" s="7" t="n">
+        <v>368.0833333333333</v>
+      </c>
+      <c r="S34" s="7" t="n">
+        <v>59.00405914179443</v>
+      </c>
+      <c r="T34" s="7" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="U34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="7" t="n">
+        <v>0.07340092752195768</v>
+      </c>
+      <c r="W34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="7" t="n">
+        <v>0.1092817779483241</v>
+      </c>
+      <c r="Y34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="7" t="n">
+        <v>46.84666666666667</v>
+      </c>
+      <c r="AA34" s="7" t="n">
+        <v>35.98333333333333</v>
+      </c>
+      <c r="AB34" s="7" t="n">
+        <v>0.7018049624302896</v>
+      </c>
+      <c r="AC34" s="7" t="n">
+        <v>0.3473404234144944</v>
+      </c>
+      <c r="AD34" s="7" t="n">
+        <v>0.8988536590113285</v>
+      </c>
+      <c r="AE34" s="7" t="n">
+        <v>0.5791688394127745</v>
+      </c>
+      <c r="AF34" s="7" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AG34" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AH34" s="7" t="n">
+        <v>0.04555431783926916</v>
+      </c>
+      <c r="AI34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="7" t="n">
+        <v>0.1175595299077914</v>
+      </c>
+      <c r="AK34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="7" t="n">
+        <v>14.68333333333333</v>
+      </c>
+      <c r="AM34" s="7" t="n">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AN34" s="7" t="n">
+        <v>1.402436801450748</v>
+      </c>
+      <c r="AO34" s="7" t="n">
+        <v>0.4545741125317043</v>
+      </c>
+      <c r="AP34" s="7" t="n">
+        <v>5.730729268130186</v>
+      </c>
+      <c r="AQ34" s="7" t="n">
+        <v>6.545867220456541</v>
+      </c>
+      <c r="AR34" s="7" t="n">
+        <v>52.48333333333333</v>
+      </c>
+      <c r="AS34" s="7" t="n">
+        <v>65.36666666666666</v>
+      </c>
+      <c r="AT34" s="7" t="n">
+        <v>43.07361049641583</v>
+      </c>
+      <c r="AU34" s="7" t="n">
+        <v>60.40870474559063</v>
+      </c>
+      <c r="AV34" s="7" t="n">
+        <v>49.24261600098349</v>
+      </c>
+      <c r="AW34" s="7" t="n">
+        <v>55.44909155638101</v>
+      </c>
+      <c r="AX34" s="7" t="n">
+        <v>45.11666666666667</v>
+      </c>
+      <c r="AY34" s="7" t="n">
+        <v>52.46666666666667</v>
+      </c>
+      <c r="AZ34" s="7" t="n">
+        <v>38.72857510577813</v>
+      </c>
+      <c r="BA34" s="7" t="n">
+        <v>48.51069404037401</v>
+      </c>
+      <c r="BB34" s="7" t="n">
+        <v>51.50456977495429</v>
+      </c>
+      <c r="BC34" s="7" t="n">
+        <v>55.47601605633623</v>
+      </c>
+      <c r="BD34" s="7" t="n">
+        <v>254.94115</v>
+      </c>
+      <c r="BE34" s="7" t="n">
+        <v>209.75</v>
+      </c>
+      <c r="BF34" s="7" t="n">
+        <v>242.4327300528639</v>
+      </c>
+      <c r="BG34" s="7" t="n">
+        <v>216.869304106342</v>
+      </c>
+      <c r="BH34" s="7" t="n">
+        <v>57.05616297397197</v>
+      </c>
+      <c r="BI34" s="7" t="n">
+        <v>62.03651130574742</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>PAIR_039</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>23:19:37</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>05:52:00</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>17:17:37</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>00:09:30</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>362</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>325.4159138009351</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>392.3709333333334</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>61.64781186469645</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>325.0535176750399</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>411.8826166666667</v>
+      </c>
+      <c r="S35" s="5" t="n">
+        <v>56.977909507314</v>
+      </c>
+      <c r="T35" s="5" t="n">
+        <v>50.36666666666667</v>
+      </c>
+      <c r="U35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="5" t="n">
+        <v>0.1423627546916193</v>
+      </c>
+      <c r="W35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="5" t="n">
+        <v>0.1695916336498443</v>
+      </c>
+      <c r="Y35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="5" t="n">
+        <v>8.366666666666667</v>
+      </c>
+      <c r="AA35" s="5" t="n">
+        <v>62.76666666666667</v>
+      </c>
+      <c r="AB35" s="5" t="n">
+        <v>0.1908765853606127</v>
+      </c>
+      <c r="AC35" s="5" t="n">
+        <v>0.9031778355480963</v>
+      </c>
+      <c r="AD35" s="5" t="n">
+        <v>1.368836070315151</v>
+      </c>
+      <c r="AE35" s="5" t="n">
+        <v>0.8633670228287695</v>
+      </c>
+      <c r="AF35" s="5" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="AG35" s="5" t="n">
+        <v>7.883333333333334</v>
+      </c>
+      <c r="AH35" s="5" t="n">
+        <v>0.1087001286100384</v>
+      </c>
+      <c r="AI35" s="5" t="n">
+        <v>0.1049872832033934</v>
+      </c>
+      <c r="AJ35" s="5" t="n">
+        <v>0.3759082257407668</v>
+      </c>
+      <c r="AK35" s="5" t="n">
+        <v>0.7990575465797383</v>
+      </c>
+      <c r="AL35" s="5" t="n">
+        <v>4.583333333333333</v>
+      </c>
+      <c r="AM35" s="5" t="n">
+        <v>2.983333333333333</v>
+      </c>
+      <c r="AN35" s="5" t="n">
+        <v>0.3780850080592794</v>
+      </c>
+      <c r="AO35" s="5" t="n">
+        <v>0.6373216143401321</v>
+      </c>
+      <c r="AP35" s="5" t="n">
+        <v>4.949476469139658</v>
+      </c>
+      <c r="AQ35" s="5" t="n">
+        <v>12.81764140572333</v>
+      </c>
+      <c r="AR35" s="5" t="n">
+        <v>74.78333333333333</v>
+      </c>
+      <c r="AS35" s="5" t="n">
+        <v>67.35806666666666</v>
+      </c>
+      <c r="AT35" s="5" t="n">
+        <v>67.00799281022444</v>
+      </c>
+      <c r="AU35" s="5" t="n">
+        <v>52.91266607635799</v>
+      </c>
+      <c r="AV35" s="5" t="n">
+        <v>53.76170584283663</v>
+      </c>
+      <c r="AW35" s="5" t="n">
+        <v>47.13258740474756</v>
+      </c>
+      <c r="AX35" s="5" t="n">
+        <v>56.4376</v>
+      </c>
+      <c r="AY35" s="5" t="n">
+        <v>47.91666666666666</v>
+      </c>
+      <c r="AZ35" s="5" t="n">
+        <v>52.06628269419153</v>
+      </c>
+      <c r="BA35" s="5" t="n">
+        <v>38.05595749464888</v>
+      </c>
+      <c r="BB35" s="5" t="n">
+        <v>55.35276060022913</v>
+      </c>
+      <c r="BC35" s="5" t="n">
+        <v>47.65267721069078</v>
+      </c>
+      <c r="BD35" s="5" t="n">
+        <v>180.4833333333333</v>
+      </c>
+      <c r="BE35" s="5" t="n">
+        <v>222.97455</v>
+      </c>
+      <c r="BF35" s="5" t="n">
+        <v>205.5216138197976</v>
+      </c>
+      <c r="BG35" s="5" t="n">
+        <v>232.4394073709414</v>
+      </c>
+      <c r="BH35" s="5" t="n">
+        <v>68.32374270489164</v>
+      </c>
+      <c r="BI35" s="5" t="n">
+        <v>62.54688906091069</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>PAIR_040</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>02-10-2026</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>23:17:00</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>05:52:00</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>23:29:56</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>04:49:26</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>12.93333333333339</v>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>326.4235517768342</v>
+      </c>
+      <c r="O36" s="7" t="n">
+        <v>395</v>
+      </c>
+      <c r="P36" s="7" t="n">
+        <v>61.32917712617816</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>325.9521091087573</v>
+      </c>
+      <c r="R36" s="7" t="n">
+        <v>319.5048166666667</v>
+      </c>
+      <c r="S36" s="7" t="n">
+        <v>62.63705094403212</v>
+      </c>
+      <c r="T36" s="7" t="n">
+        <v>50.36666666666667</v>
+      </c>
+      <c r="U36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="7" t="n">
+        <v>0.1423627546916193</v>
+      </c>
+      <c r="W36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="7" t="n">
+        <v>0.1695916336498443</v>
+      </c>
+      <c r="Y36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="7" t="n">
+        <v>8.366666666666667</v>
+      </c>
+      <c r="AA36" s="7" t="n">
+        <v>3.016666666666667</v>
+      </c>
+      <c r="AB36" s="7" t="n">
+        <v>0.1908765853606127</v>
+      </c>
+      <c r="AC36" s="7" t="n">
+        <v>0.002166493188354733</v>
+      </c>
+      <c r="AD36" s="7" t="n">
+        <v>1.368836070315151</v>
+      </c>
+      <c r="AE36" s="7" t="n">
+        <v>0.04309047225456927</v>
+      </c>
+      <c r="AF36" s="7" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="AG36" s="7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH36" s="7" t="n">
+        <v>0.1087001286100384</v>
+      </c>
+      <c r="AI36" s="7" t="n">
+        <v>0.04085835435001741</v>
+      </c>
+      <c r="AJ36" s="7" t="n">
+        <v>0.3759082257407668</v>
+      </c>
+      <c r="AK36" s="7" t="n">
+        <v>0.5701165723258244</v>
+      </c>
+      <c r="AL36" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AM36" s="7" t="n">
+        <v>1.883333333333333</v>
+      </c>
+      <c r="AN36" s="7" t="n">
+        <v>0.398684318669226</v>
+      </c>
+      <c r="AO36" s="7" t="n">
+        <v>0.3612962495734293</v>
+      </c>
+      <c r="AP36" s="7" t="n">
+        <v>5.036012446348118</v>
+      </c>
+      <c r="AQ36" s="7" t="n">
+        <v>11.5103229952597</v>
+      </c>
+      <c r="AR36" s="7" t="n">
+        <v>75.68333333333334</v>
+      </c>
+      <c r="AS36" s="7" t="n">
+        <v>49.16666666666666</v>
+      </c>
+      <c r="AT36" s="7" t="n">
+        <v>67.35824904037362</v>
+      </c>
+      <c r="AU36" s="7" t="n">
+        <v>42.50561741506265</v>
+      </c>
+      <c r="AV36" s="7" t="n">
+        <v>53.4000653039738</v>
+      </c>
+      <c r="AW36" s="7" t="n">
+        <v>51.87126193024596</v>
+      </c>
+      <c r="AX36" s="7" t="n">
+        <v>57.18333333333333</v>
+      </c>
+      <c r="AY36" s="7" t="n">
+        <v>35.33333333333334</v>
+      </c>
+      <c r="AZ36" s="7" t="n">
+        <v>52.27381680184341</v>
+      </c>
+      <c r="BA36" s="7" t="n">
+        <v>30.72869553457691</v>
+      </c>
+      <c r="BB36" s="7" t="n">
+        <v>54.84865651024083</v>
+      </c>
+      <c r="BC36" s="7" t="n">
+        <v>52.18080373796077</v>
+      </c>
+      <c r="BD36" s="7" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="BE36" s="7" t="n">
+        <v>225.8048166666667</v>
+      </c>
+      <c r="BF36" s="7" t="n">
+        <v>205.9508621472857</v>
+      </c>
+      <c r="BG36" s="7" t="n">
+        <v>252.313475062006</v>
+      </c>
+      <c r="BH36" s="7" t="n">
+        <v>68.15803490809235</v>
+      </c>
+      <c r="BI36" s="7" t="n">
+        <v>67.04378023108464</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>PAIR_041</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>02-10-2026</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>23:13:07</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>05:06:58</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>23:27:11</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>05:39:44</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>14.06666666666683</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>325.4492993959398</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>353.84785</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>67.12149214202077</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>325.1974783974341</v>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>372.5504</v>
+      </c>
+      <c r="S37" s="5" t="n">
+        <v>59.84310713127186</v>
+      </c>
+      <c r="T37" s="5" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="U37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="5" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+      <c r="W37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="5" t="n">
+        <v>0.07012377305626648</v>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="5" t="n">
+        <v>6.683333333333334</v>
+      </c>
+      <c r="AA37" s="5" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="AB37" s="5" t="n">
+        <v>0.1270140960027041</v>
+      </c>
+      <c r="AC37" s="5" t="n">
+        <v>0.54761889554039</v>
+      </c>
+      <c r="AD37" s="5" t="n">
+        <v>1.140276173590361</v>
+      </c>
+      <c r="AE37" s="5" t="n">
+        <v>0.7703900054495522</v>
+      </c>
+      <c r="AF37" s="5" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AG37" s="5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AH37" s="5" t="n">
+        <v>0.03154860869050958</v>
+      </c>
+      <c r="AI37" s="5" t="n">
+        <v>0.050473616639225</v>
+      </c>
+      <c r="AJ37" s="5" t="n">
+        <v>0.1610992784196234</v>
+      </c>
+      <c r="AK37" s="5" t="n">
+        <v>0.6805431456974156</v>
+      </c>
+      <c r="AL37" s="5" t="n">
+        <v>2.016666666666667</v>
+      </c>
+      <c r="AM37" s="5" t="n">
+        <v>12.01666666666667</v>
+      </c>
+      <c r="AN37" s="5" t="n">
+        <v>0.1675031909150123</v>
+      </c>
+      <c r="AO37" s="5" t="n">
+        <v>0.9451362793530877</v>
+      </c>
+      <c r="AP37" s="5" t="n">
+        <v>4.98356601069458</v>
+      </c>
+      <c r="AQ37" s="5" t="n">
+        <v>4.719127053635388</v>
+      </c>
+      <c r="AR37" s="5" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AS37" s="5" t="n">
+        <v>56.91666666666666</v>
+      </c>
+      <c r="AT37" s="5" t="n">
+        <v>59.99350553918008</v>
+      </c>
+      <c r="AU37" s="5" t="n">
+        <v>50.23554888844169</v>
+      </c>
+      <c r="AV37" s="5" t="n">
+        <v>55.98149817030801</v>
+      </c>
+      <c r="AW37" s="5" t="n">
+        <v>52.95694758371599</v>
+      </c>
+      <c r="AX37" s="5" t="n">
+        <v>51.86666666666667</v>
+      </c>
+      <c r="AY37" s="5" t="n">
+        <v>49.01706666666666</v>
+      </c>
+      <c r="AZ37" s="5" t="n">
+        <v>53.82311966809345</v>
+      </c>
+      <c r="BA37" s="5" t="n">
+        <v>45.36220285483913</v>
+      </c>
+      <c r="BB37" s="5" t="n">
+        <v>62.26324897337287</v>
+      </c>
+      <c r="BC37" s="5" t="n">
+        <v>55.52621477329696</v>
+      </c>
+      <c r="BD37" s="5" t="n">
+        <v>172.54785</v>
+      </c>
+      <c r="BE37" s="5" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="BF37" s="5" t="n">
+        <v>211.2543855609569</v>
+      </c>
+      <c r="BG37" s="5" t="n">
+        <v>228.0564978626206</v>
+      </c>
+      <c r="BH37" s="5" t="n">
+        <v>73.45940928071497</v>
+      </c>
+      <c r="BI37" s="5" t="n">
+        <v>65.94404757473367</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>PAIR_043</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
           <t>Madiwala to Madhuravoyal</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>Madiwala to Madhuravoyal</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>20-09-2026</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>13-09-2026</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>16:17:59</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>22:40:31</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>06:06:58</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>12:12:58</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>17:54:24</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="n">
+        <v>627.55</v>
+      </c>
+      <c r="N38" s="7" t="n">
+        <v>322.1774743037008</v>
+      </c>
+      <c r="O38" s="7" t="n">
+        <v>446.45</v>
+      </c>
+      <c r="P38" s="7" t="n">
+        <v>64.4401967523076</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>321.6269481176106</v>
+      </c>
+      <c r="R38" s="7" t="n">
+        <v>341.4423833333333</v>
+      </c>
+      <c r="S38" s="7" t="n">
+        <v>64.28145295102571</v>
+      </c>
+      <c r="T38" s="7" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="U38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="7" t="n">
+        <v>0.1119717603069536</v>
+      </c>
+      <c r="W38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="7" t="n">
+        <v>0.10630230408888</v>
+      </c>
+      <c r="Y38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="7" t="n">
+        <v>51.31666666666667</v>
+      </c>
+      <c r="AA38" s="7" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="AB38" s="7" t="n">
+        <v>0.2137910036648912</v>
+      </c>
+      <c r="AC38" s="7" t="n">
+        <v>0.4503679422720615</v>
+      </c>
+      <c r="AD38" s="7" t="n">
+        <v>0.2499667467338773</v>
+      </c>
+      <c r="AE38" s="7" t="n">
+        <v>0.7633354953763755</v>
+      </c>
+      <c r="AF38" s="7" t="n">
+        <v>32.28333333333333</v>
+      </c>
+      <c r="AG38" s="7" t="n">
+        <v>6.316666666666666</v>
+      </c>
+      <c r="AH38" s="7" t="n">
+        <v>0.0266289259127734</v>
+      </c>
+      <c r="AI38" s="7" t="n">
+        <v>0.06317093999191636</v>
+      </c>
+      <c r="AJ38" s="7" t="n">
+        <v>0.04949103422095211</v>
+      </c>
+      <c r="AK38" s="7" t="n">
+        <v>0.6000405909522399</v>
+      </c>
+      <c r="AL38" s="7" t="n">
+        <v>7.716666666666667</v>
+      </c>
+      <c r="AM38" s="7" t="n">
+        <v>10.01666666666667</v>
+      </c>
+      <c r="AN38" s="7" t="n">
+        <v>0.5319201203612787</v>
+      </c>
+      <c r="AO38" s="7" t="n">
+        <v>0.8996597832386584</v>
+      </c>
+      <c r="AP38" s="7" t="n">
+        <v>4.13587998553046</v>
+      </c>
+      <c r="AQ38" s="7" t="n">
+        <v>5.388977070980315</v>
+      </c>
+      <c r="AR38" s="7" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AS38" s="7" t="n">
+        <v>63.38333333333333</v>
+      </c>
+      <c r="AT38" s="7" t="n">
+        <v>67.23521804769611</v>
+      </c>
+      <c r="AU38" s="7" t="n">
+        <v>58.37602971556508</v>
+      </c>
+      <c r="AV38" s="7" t="n">
+        <v>58.12843058878625</v>
+      </c>
+      <c r="AW38" s="7" t="n">
+        <v>55.25998079832614</v>
+      </c>
+      <c r="AX38" s="7" t="n">
+        <v>57.93333333333333</v>
+      </c>
+      <c r="AY38" s="7" t="n">
+        <v>44.56666666666667</v>
+      </c>
+      <c r="AZ38" s="7" t="n">
+        <v>56.31975683439349</v>
+      </c>
+      <c r="BA38" s="7" t="n">
+        <v>42.97209112540976</v>
+      </c>
+      <c r="BB38" s="7" t="n">
+        <v>58.32886208395183</v>
+      </c>
+      <c r="BC38" s="7" t="n">
+        <v>57.85322664602661</v>
+      </c>
+      <c r="BD38" s="7" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="BE38" s="7" t="n">
+        <v>181.75905</v>
+      </c>
+      <c r="BF38" s="7" t="n">
+        <v>197.7381876113653</v>
+      </c>
+      <c r="BG38" s="7" t="n">
+        <v>218.8656286111331</v>
+      </c>
+      <c r="BH38" s="7" t="n">
+        <v>72.07953375869938</v>
+      </c>
+      <c r="BI38" s="7" t="n">
+        <v>72.24915467300245</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>PAIR_044</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>20-09-2026</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>11:26:04</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>18:14:41</t>
         </is>
       </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>02:45:02</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>23:17:34</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>04:42:50</t>
         </is>
       </c>
-      <c r="L32" s="6" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M32" s="7" t="n">
-        <v>627.05</v>
-      </c>
-      <c r="N32" s="7" t="n">
-        <v>106.4407237351212</v>
-      </c>
-      <c r="O32" s="7" t="n">
-        <v>116.7043666666667</v>
-      </c>
-      <c r="P32" s="7" t="n">
-        <v>57.74313792935574</v>
-      </c>
-      <c r="Q32" s="7" t="n">
-        <v>106.429493371315</v>
-      </c>
-      <c r="R32" s="7" t="n">
-        <v>117.7956</v>
-      </c>
-      <c r="S32" s="7" t="n">
-        <v>61.22560386453947</v>
-      </c>
-      <c r="T32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="7" t="n">
-        <v>13.68333333333333</v>
-      </c>
-      <c r="AB32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="7" t="n">
-        <v>0.1905534317712249</v>
-      </c>
-      <c r="AD32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="7" t="n">
-        <v>0.8355570698860046</v>
-      </c>
-      <c r="AF32" s="7" t="n">
-        <v>6.166666666666667</v>
-      </c>
-      <c r="AG32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="7" t="n">
-        <v>0.06082944355873176</v>
-      </c>
-      <c r="AI32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="7" t="n">
-        <v>0.5918540454363089</v>
-      </c>
-      <c r="AK32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" s="7" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AM32" s="7" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AN32" s="7" t="n">
-        <v>0.07885964335257711</v>
-      </c>
-      <c r="AO32" s="7" t="n">
-        <v>0.005855051964785372</v>
-      </c>
-      <c r="AP32" s="7" t="n">
-        <v>7.09736790173194</v>
-      </c>
-      <c r="AQ32" s="7" t="n">
-        <v>1.053909353661367</v>
-      </c>
-      <c r="AR32" s="7" t="n">
-        <v>32.13333333333333</v>
-      </c>
-      <c r="AS32" s="7" t="n">
-        <v>15.36666666666667</v>
-      </c>
-      <c r="AT32" s="7" t="n">
-        <v>27.22400876286396</v>
-      </c>
-      <c r="AU32" s="7" t="n">
-        <v>12.99028801976566</v>
-      </c>
-      <c r="AV32" s="7" t="n">
-        <v>50.83321138294101</v>
-      </c>
-      <c r="AW32" s="7" t="n">
-        <v>50.72129812489845</v>
-      </c>
-      <c r="AX32" s="7" t="n">
-        <v>25.45</v>
-      </c>
-      <c r="AY32" s="7" t="n">
-        <v>12.98333333333333</v>
-      </c>
-      <c r="AZ32" s="7" t="n">
-        <v>21.71770276874582</v>
-      </c>
-      <c r="BA32" s="7" t="n">
-        <v>11.46884073038654</v>
-      </c>
-      <c r="BB32" s="7" t="n">
-        <v>51.20087096757365</v>
-      </c>
-      <c r="BC32" s="7" t="n">
-        <v>53.00106114170931</v>
-      </c>
-      <c r="BD32" s="7" t="n">
-        <v>52.2877</v>
-      </c>
-      <c r="BE32" s="7" t="n">
-        <v>75.42893333333333</v>
-      </c>
-      <c r="BF32" s="7" t="n">
-        <v>57.35932311660007</v>
-      </c>
-      <c r="BG32" s="7" t="n">
-        <v>81.77395613742682</v>
-      </c>
-      <c r="BH32" s="7" t="n">
-        <v>65.81967435928536</v>
-      </c>
-      <c r="BI32" s="7" t="n">
-        <v>65.04715301439072</v>
+      <c r="M39" s="5" t="n">
+        <v>711.4999999999999</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>324.4297883243897</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>408.6267666666666</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>62.28065772239027</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>325.0350667285441</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>325.2655</v>
+      </c>
+      <c r="S39" s="5" t="n">
+        <v>63.75914065702941</v>
+      </c>
+      <c r="T39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="5" t="n">
+        <v>65.98333333333333</v>
+      </c>
+      <c r="AA39" s="5" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AB39" s="5" t="n">
+        <v>0.2402194601328752</v>
+      </c>
+      <c r="AC39" s="5" t="n">
+        <v>0.3478638485950774</v>
+      </c>
+      <c r="AD39" s="5" t="n">
+        <v>0.2184364881228469</v>
+      </c>
+      <c r="AE39" s="5" t="n">
+        <v>1.235019580810926</v>
+      </c>
+      <c r="AF39" s="5" t="n">
+        <v>30.53333333333333</v>
+      </c>
+      <c r="AG39" s="5" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="AH39" s="5" t="n">
+        <v>0.2158637009068103</v>
+      </c>
+      <c r="AI39" s="5" t="n">
+        <v>0.0127297174998127</v>
+      </c>
+      <c r="AJ39" s="5" t="n">
+        <v>0.4241863118256098</v>
+      </c>
+      <c r="AK39" s="5" t="n">
+        <v>0.2695704882313278</v>
+      </c>
+      <c r="AL39" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AM39" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN39" s="5" t="n">
+        <v>0.5924866771054754</v>
+      </c>
+      <c r="AO39" s="5" t="n">
+        <v>0.4202840859765154</v>
+      </c>
+      <c r="AP39" s="5" t="n">
+        <v>5.642730258147385</v>
+      </c>
+      <c r="AQ39" s="5" t="n">
+        <v>6.304261289647731</v>
+      </c>
+      <c r="AR39" s="5" t="n">
+        <v>75.78333333333333</v>
+      </c>
+      <c r="AS39" s="5" t="n">
+        <v>46.73333333333333</v>
+      </c>
+      <c r="AT39" s="5" t="n">
+        <v>70.97085214069388</v>
+      </c>
+      <c r="AU39" s="5" t="n">
+        <v>41.50209986904579</v>
+      </c>
+      <c r="AV39" s="5" t="n">
+        <v>56.18981035990718</v>
+      </c>
+      <c r="AW39" s="5" t="n">
+        <v>53.28372308436693</v>
+      </c>
+      <c r="AX39" s="5" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="AY39" s="5" t="n">
+        <v>34.78333333333333</v>
+      </c>
+      <c r="AZ39" s="5" t="n">
+        <v>57.38992771876193</v>
+      </c>
+      <c r="BA39" s="5" t="n">
+        <v>32.23439151995442</v>
+      </c>
+      <c r="BB39" s="5" t="n">
+        <v>57.77509501888785</v>
+      </c>
+      <c r="BC39" s="5" t="n">
+        <v>55.60316697260945</v>
+      </c>
+      <c r="BD39" s="5" t="n">
+        <v>170.4267666666667</v>
+      </c>
+      <c r="BE39" s="5" t="n">
+        <v>220.0155</v>
+      </c>
+      <c r="BF39" s="5" t="n">
+        <v>195.0204386267887</v>
+      </c>
+      <c r="BG39" s="5" t="n">
+        <v>250.5176976874725</v>
+      </c>
+      <c r="BH39" s="5" t="n">
+        <v>68.65838357711408</v>
+      </c>
+      <c r="BI39" s="5" t="n">
+        <v>68.31819513283541</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>PAIR_045</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>03-10-2026</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>22:40:31</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>06:06:58</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>22:00:02</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>03:49:27</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="n">
+        <v>40.48333333333335</v>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>322.2735940834601</v>
+      </c>
+      <c r="O40" s="7" t="n">
+        <v>446.45</v>
+      </c>
+      <c r="P40" s="7" t="n">
+        <v>64.45944316240457</v>
+      </c>
+      <c r="Q40" s="7" t="n">
+        <v>322.6469826189222</v>
+      </c>
+      <c r="R40" s="7" t="n">
+        <v>349.4259833333334</v>
+      </c>
+      <c r="S40" s="7" t="n">
+        <v>59.87583735700611</v>
+      </c>
+      <c r="T40" s="7" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="U40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="7" t="n">
+        <v>0.1119717603069536</v>
+      </c>
+      <c r="W40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="7" t="n">
+        <v>0.10630230408888</v>
+      </c>
+      <c r="Y40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="7" t="n">
+        <v>51.31666666666667</v>
+      </c>
+      <c r="AA40" s="7" t="n">
+        <v>24.31666666666667</v>
+      </c>
+      <c r="AB40" s="7" t="n">
+        <v>0.2137910036648912</v>
+      </c>
+      <c r="AC40" s="7" t="n">
+        <v>0.4433224105129225</v>
+      </c>
+      <c r="AD40" s="7" t="n">
+        <v>0.2499667467338773</v>
+      </c>
+      <c r="AE40" s="7" t="n">
+        <v>1.093872980018177</v>
+      </c>
+      <c r="AF40" s="7" t="n">
+        <v>32.28333333333333</v>
+      </c>
+      <c r="AG40" s="7" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AH40" s="7" t="n">
+        <v>0.0266289259127734</v>
+      </c>
+      <c r="AI40" s="7" t="n">
+        <v>0.428265735708522</v>
+      </c>
+      <c r="AJ40" s="7" t="n">
+        <v>0.04949103422095211</v>
+      </c>
+      <c r="AK40" s="7" t="n">
+        <v>9.635979053441744</v>
+      </c>
+      <c r="AL40" s="7" t="n">
+        <v>7.716666666666667</v>
+      </c>
+      <c r="AM40" s="7" t="n">
+        <v>5.683333333333334</v>
+      </c>
+      <c r="AN40" s="7" t="n">
+        <v>0.5621573347884641</v>
+      </c>
+      <c r="AO40" s="7" t="n">
+        <v>0.5110447249900278</v>
+      </c>
+      <c r="AP40" s="7" t="n">
+        <v>4.37098575645458</v>
+      </c>
+      <c r="AQ40" s="7" t="n">
+        <v>5.395193577607332</v>
+      </c>
+      <c r="AR40" s="7" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AS40" s="7" t="n">
+        <v>44.13333333333333</v>
+      </c>
+      <c r="AT40" s="7" t="n">
+        <v>67.30110061302815</v>
+      </c>
+      <c r="AU40" s="7" t="n">
+        <v>36.19726417049096</v>
+      </c>
+      <c r="AV40" s="7" t="n">
+        <v>58.18538957898687</v>
+      </c>
+      <c r="AW40" s="7" t="n">
+        <v>49.21078210489708</v>
+      </c>
+      <c r="AX40" s="7" t="n">
+        <v>57.93333333333333</v>
+      </c>
+      <c r="AY40" s="7" t="n">
+        <v>32.11666666666667</v>
+      </c>
+      <c r="AZ40" s="7" t="n">
+        <v>56.31975683439349</v>
+      </c>
+      <c r="BA40" s="7" t="n">
+        <v>28.87956171842685</v>
+      </c>
+      <c r="BB40" s="7" t="n">
+        <v>58.32886208395183</v>
+      </c>
+      <c r="BC40" s="7" t="n">
+        <v>53.95247648486594</v>
+      </c>
+      <c r="BD40" s="7" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="BE40" s="7" t="n">
+        <v>240.5093166666666</v>
+      </c>
+      <c r="BF40" s="7" t="n">
+        <v>197.7381876113653</v>
+      </c>
+      <c r="BG40" s="7" t="n">
+        <v>256.1875238587929</v>
+      </c>
+      <c r="BH40" s="7" t="n">
+        <v>72.07953375869938</v>
+      </c>
+      <c r="BI40" s="7" t="n">
+        <v>63.91125152474375</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>PAIR_046</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>03-10-2026</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>22:22:51</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>04:57:29</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>23:13:05</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>04:42:50</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>50.23333333333335</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>324.9350283808783</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>394.6350333333333</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>64.17415185678969</v>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>325.7263480402497</v>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="S41" s="5" t="n">
+        <v>63.70255625065911</v>
+      </c>
+      <c r="T41" s="5" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="U41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="5" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+      <c r="W41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="5" t="n">
+        <v>0.1531911902360135</v>
+      </c>
+      <c r="Y41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="5" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="AA41" s="5" t="n">
+        <v>20.58333333333333</v>
+      </c>
+      <c r="AB41" s="5" t="n">
+        <v>0.1794253337608642</v>
+      </c>
+      <c r="AC41" s="5" t="n">
+        <v>0.4766783541068861</v>
+      </c>
+      <c r="AD41" s="5" t="n">
+        <v>0.2874638191095287</v>
+      </c>
+      <c r="AE41" s="5" t="n">
+        <v>1.389507752862178</v>
+      </c>
+      <c r="AF41" s="5" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="AG41" s="5" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="AH41" s="5" t="n">
+        <v>0.05059730733317578</v>
+      </c>
+      <c r="AI41" s="5" t="n">
+        <v>0.0127297174998127</v>
+      </c>
+      <c r="AJ41" s="5" t="n">
+        <v>0.161052437134777</v>
+      </c>
+      <c r="AK41" s="5" t="n">
+        <v>0.2695704882313278</v>
+      </c>
+      <c r="AL41" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM41" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN41" s="5" t="n">
+        <v>0.5766516264825126</v>
+      </c>
+      <c r="AO41" s="5" t="n">
+        <v>0.4202840859765154</v>
+      </c>
+      <c r="AP41" s="5" t="n">
+        <v>4.324887198618844</v>
+      </c>
+      <c r="AQ41" s="5" t="n">
+        <v>6.304261289647731</v>
+      </c>
+      <c r="AR41" s="5" t="n">
+        <v>64.65921666666667</v>
+      </c>
+      <c r="AS41" s="5" t="n">
+        <v>46.73333333333333</v>
+      </c>
+      <c r="AT41" s="5" t="n">
+        <v>63.80717597571496</v>
+      </c>
+      <c r="AU41" s="5" t="n">
+        <v>41.50209986904579</v>
+      </c>
+      <c r="AV41" s="5" t="n">
+        <v>59.20935569447663</v>
+      </c>
+      <c r="AW41" s="5" t="n">
+        <v>53.28372308436693</v>
+      </c>
+      <c r="AX41" s="5" t="n">
+        <v>54.06666666666667</v>
+      </c>
+      <c r="AY41" s="5" t="n">
+        <v>35.11666666666667</v>
+      </c>
+      <c r="AZ41" s="5" t="n">
+        <v>54.00426203304914</v>
+      </c>
+      <c r="BA41" s="5" t="n">
+        <v>32.50454485672611</v>
+      </c>
+      <c r="BB41" s="5" t="n">
+        <v>59.93074701571421</v>
+      </c>
+      <c r="BC41" s="5" t="n">
+        <v>55.53695371818415</v>
+      </c>
+      <c r="BD41" s="5" t="n">
+        <v>176.7758166666667</v>
+      </c>
+      <c r="BE41" s="5" t="n">
+        <v>220.4833333333333</v>
+      </c>
+      <c r="BF41" s="5" t="n">
+        <v>206.2279801079839</v>
+      </c>
+      <c r="BG41" s="5" t="n">
+        <v>250.8100111568945</v>
+      </c>
+      <c r="BH41" s="5" t="n">
+        <v>69.99644544033519</v>
+      </c>
+      <c r="BI41" s="5" t="n">
+        <v>68.25278102387333</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>PAIR_047</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>02-10-2026</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>23:13:07</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>05:06:58</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>17:14:54</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>00:07:23</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="n">
+        <v>358.2166666666665</v>
+      </c>
+      <c r="N42" s="7" t="n">
+        <v>325.3816512944114</v>
+      </c>
+      <c r="O42" s="7" t="n">
+        <v>353.84785</v>
+      </c>
+      <c r="P42" s="7" t="n">
+        <v>67.10753118315435</v>
+      </c>
+      <c r="Q42" s="7" t="n">
+        <v>325.1731293793417</v>
+      </c>
+      <c r="R42" s="7" t="n">
+        <v>412.4881333333333</v>
+      </c>
+      <c r="S42" s="7" t="n">
+        <v>57.06712981492286</v>
+      </c>
+      <c r="T42" s="7" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="U42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="7" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+      <c r="W42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="7" t="n">
+        <v>0.07012377305626648</v>
+      </c>
+      <c r="Y42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="7" t="n">
+        <v>6.683333333333334</v>
+      </c>
+      <c r="AA42" s="7" t="n">
+        <v>62.76666666666667</v>
+      </c>
+      <c r="AB42" s="7" t="n">
+        <v>0.1270140960027041</v>
+      </c>
+      <c r="AC42" s="7" t="n">
+        <v>0.9031778355480963</v>
+      </c>
+      <c r="AD42" s="7" t="n">
+        <v>1.140276173590361</v>
+      </c>
+      <c r="AE42" s="7" t="n">
+        <v>0.8633670228287695</v>
+      </c>
+      <c r="AF42" s="7" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AG42" s="7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AH42" s="7" t="n">
+        <v>0.03154860869050958</v>
+      </c>
+      <c r="AI42" s="7" t="n">
+        <v>0.108236844142404</v>
+      </c>
+      <c r="AJ42" s="7" t="n">
+        <v>0.1610992784196234</v>
+      </c>
+      <c r="AK42" s="7" t="n">
+        <v>0.729686589724072</v>
+      </c>
+      <c r="AL42" s="7" t="n">
+        <v>2.016666666666667</v>
+      </c>
+      <c r="AM42" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AN42" s="7" t="n">
+        <v>0.1675031909150123</v>
+      </c>
+      <c r="AO42" s="7" t="n">
+        <v>0.6481534841388865</v>
+      </c>
+      <c r="AP42" s="7" t="n">
+        <v>4.98356601069458</v>
+      </c>
+      <c r="AQ42" s="7" t="n">
+        <v>11.78460880252521</v>
+      </c>
+      <c r="AR42" s="7" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AS42" s="7" t="n">
+        <v>67.36666666666666</v>
+      </c>
+      <c r="AT42" s="7" t="n">
+        <v>59.94580589720089</v>
+      </c>
+      <c r="AU42" s="7" t="n">
+        <v>52.96068060572409</v>
+      </c>
+      <c r="AV42" s="7" t="n">
+        <v>55.93698839552183</v>
+      </c>
+      <c r="AW42" s="7" t="n">
+        <v>47.16933453255981</v>
+      </c>
+      <c r="AX42" s="7" t="n">
+        <v>51.86666666666667</v>
+      </c>
+      <c r="AY42" s="7" t="n">
+        <v>48.23333333333333</v>
+      </c>
+      <c r="AZ42" s="7" t="n">
+        <v>53.82311966809345</v>
+      </c>
+      <c r="BA42" s="7" t="n">
+        <v>38.3638733890867</v>
+      </c>
+      <c r="BB42" s="7" t="n">
+        <v>62.26324897337287</v>
+      </c>
+      <c r="BC42" s="7" t="n">
+        <v>47.72285563258885</v>
+      </c>
+      <c r="BD42" s="7" t="n">
+        <v>172.54785</v>
+      </c>
+      <c r="BE42" s="7" t="n">
+        <v>221.9214666666667</v>
+      </c>
+      <c r="BF42" s="7" t="n">
+        <v>211.2344371014078</v>
+      </c>
+      <c r="BG42" s="7" t="n">
+        <v>232.1890072207015</v>
+      </c>
+      <c r="BH42" s="7" t="n">
+        <v>73.45247261026125</v>
+      </c>
+      <c r="BI42" s="7" t="n">
+        <v>62.77599297848649</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>PAIR_049</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>20-09-2026</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>03-10-2026</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>11:26:04</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>18:13:48</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>22:06:43</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>03:52:46</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>640.65</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>323.753642085549</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>407.74795</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>62.32616891116043</v>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>324.1251397273161</v>
+      </c>
+      <c r="R43" s="5" t="n">
+        <v>346.04665</v>
+      </c>
+      <c r="S43" s="5" t="n">
+        <v>60.09883681712126</v>
+      </c>
+      <c r="T43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="5" t="n">
+        <v>65.98333333333333</v>
+      </c>
+      <c r="AA43" s="5" t="n">
+        <v>20.63333333333333</v>
+      </c>
+      <c r="AB43" s="5" t="n">
+        <v>0.2402194601328752</v>
+      </c>
+      <c r="AC43" s="5" t="n">
+        <v>0.4185697978984132</v>
+      </c>
+      <c r="AD43" s="5" t="n">
+        <v>0.2184364881228469</v>
+      </c>
+      <c r="AE43" s="5" t="n">
+        <v>1.217165809720749</v>
+      </c>
+      <c r="AF43" s="5" t="n">
+        <v>30.53333333333333</v>
+      </c>
+      <c r="AG43" s="5" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AH43" s="5" t="n">
+        <v>0.2158637009068103</v>
+      </c>
+      <c r="AI43" s="5" t="n">
+        <v>0.428265735708522</v>
+      </c>
+      <c r="AJ43" s="5" t="n">
+        <v>0.4241863118256098</v>
+      </c>
+      <c r="AK43" s="5" t="n">
+        <v>9.635979053441744</v>
+      </c>
+      <c r="AL43" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AM43" s="5" t="n">
+        <v>5.016666666666667</v>
+      </c>
+      <c r="AN43" s="5" t="n">
+        <v>0.5924866771054754</v>
+      </c>
+      <c r="AO43" s="5" t="n">
+        <v>0.4666024413592124</v>
+      </c>
+      <c r="AP43" s="5" t="n">
+        <v>5.642730258147385</v>
+      </c>
+      <c r="AQ43" s="5" t="n">
+        <v>5.580627205625132</v>
+      </c>
+      <c r="AR43" s="5" t="n">
+        <v>75.51461666666667</v>
+      </c>
+      <c r="AS43" s="5" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="AT43" s="5" t="n">
+        <v>70.78420748683264</v>
+      </c>
+      <c r="AU43" s="5" t="n">
+        <v>35.97418131675639</v>
+      </c>
+      <c r="AV43" s="5" t="n">
+        <v>56.24146207292706</v>
+      </c>
+      <c r="AW43" s="5" t="n">
+        <v>50.08006679826876</v>
+      </c>
+      <c r="AX43" s="5" t="n">
+        <v>59.38333333333333</v>
+      </c>
+      <c r="AY43" s="5" t="n">
+        <v>32.11666666666667</v>
+      </c>
+      <c r="AZ43" s="5" t="n">
+        <v>57.21717097154523</v>
+      </c>
+      <c r="BA43" s="5" t="n">
+        <v>28.82664857731616</v>
+      </c>
+      <c r="BB43" s="5" t="n">
+        <v>57.81134310905496</v>
+      </c>
+      <c r="BC43" s="5" t="n">
+        <v>53.85362474226164</v>
+      </c>
+      <c r="BD43" s="5" t="n">
+        <v>170.0333333333333</v>
+      </c>
+      <c r="BE43" s="5" t="n">
+        <v>242.5133166666667</v>
+      </c>
+      <c r="BF43" s="5" t="n">
+        <v>194.703693789026</v>
+      </c>
+      <c r="BG43" s="5" t="n">
+        <v>258.0108718582774</v>
+      </c>
+      <c r="BH43" s="5" t="n">
+        <v>68.70547908650204</v>
+      </c>
+      <c r="BI43" s="5" t="n">
+        <v>63.83423609176366</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>PAIR_050</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>03-10-2026</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>20-09-2026</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>21:59:13</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>04:59:52</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>12:12:58</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>18:04:43</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>586.25</v>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>326.4659622430934</v>
+      </c>
+      <c r="O44" s="7" t="n">
+        <v>420.64665</v>
+      </c>
+      <c r="P44" s="7" t="n">
+        <v>63.92417977688259</v>
+      </c>
+      <c r="Q44" s="7" t="n">
+        <v>326.1341423944449</v>
+      </c>
+      <c r="R44" s="7" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="S44" s="7" t="n">
+        <v>63.01656664035327</v>
+      </c>
+      <c r="T44" s="7" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="U44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="7" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+      <c r="W44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="7" t="n">
+        <v>0.1531911902360135</v>
+      </c>
+      <c r="Y44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="7" t="n">
+        <v>58.16666666666666</v>
+      </c>
+      <c r="AA44" s="7" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="AB44" s="7" t="n">
+        <v>0.3279316256974203</v>
+      </c>
+      <c r="AC44" s="7" t="n">
+        <v>0.4503679422720615</v>
+      </c>
+      <c r="AD44" s="7" t="n">
+        <v>0.3382675795159636</v>
+      </c>
+      <c r="AE44" s="7" t="n">
+        <v>0.7633354953763755</v>
+      </c>
+      <c r="AF44" s="7" t="n">
+        <v>21.67998333333333</v>
+      </c>
+      <c r="AG44" s="7" t="n">
+        <v>6.316666666666666</v>
+      </c>
+      <c r="AH44" s="7" t="n">
+        <v>0.07129119195051567</v>
+      </c>
+      <c r="AI44" s="7" t="n">
+        <v>0.06317093999191636</v>
+      </c>
+      <c r="AJ44" s="7" t="n">
+        <v>0.1973004984027943</v>
+      </c>
+      <c r="AK44" s="7" t="n">
+        <v>0.6000405909522399</v>
+      </c>
+      <c r="AL44" s="7" t="n">
+        <v>8.083333333333334</v>
+      </c>
+      <c r="AM44" s="7" t="n">
+        <v>10.68333333333333</v>
+      </c>
+      <c r="AN44" s="7" t="n">
+        <v>0.5879855152386801</v>
+      </c>
+      <c r="AO44" s="7" t="n">
+        <v>0.9301404042363888</v>
+      </c>
+      <c r="AP44" s="7" t="n">
+        <v>4.364428566720099</v>
+      </c>
+      <c r="AQ44" s="7" t="n">
+        <v>5.223877465290172</v>
+      </c>
+      <c r="AR44" s="7" t="n">
+        <v>65.96666666666667</v>
+      </c>
+      <c r="AS44" s="7" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="AT44" s="7" t="n">
+        <v>64.43671090657982</v>
+      </c>
+      <c r="AU44" s="7" t="n">
+        <v>59.92188649758575</v>
+      </c>
+      <c r="AV44" s="7" t="n">
+        <v>58.60842831321055</v>
+      </c>
+      <c r="AW44" s="7" t="n">
+        <v>54.39203010370871</v>
+      </c>
+      <c r="AX44" s="7" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AY44" s="7" t="n">
+        <v>47.53333333333333</v>
+      </c>
+      <c r="AZ44" s="7" t="n">
+        <v>54.47632725636674</v>
+      </c>
+      <c r="BA44" s="7" t="n">
+        <v>44.51480319122793</v>
+      </c>
+      <c r="BB44" s="7" t="n">
+        <v>59.64561378434314</v>
+      </c>
+      <c r="BC44" s="7" t="n">
+        <v>56.18979364951632</v>
+      </c>
+      <c r="BD44" s="7" t="n">
+        <v>177.1166666666667</v>
+      </c>
+      <c r="BE44" s="7" t="n">
+        <v>185.7166666666667</v>
+      </c>
+      <c r="BF44" s="7" t="n">
+        <v>206.4767797507066</v>
+      </c>
+      <c r="BG44" s="7" t="n">
+        <v>220.2537734191309</v>
+      </c>
+      <c r="BH44" s="7" t="n">
+        <v>69.94602494613189</v>
+      </c>
+      <c r="BI44" s="7" t="n">
+        <v>71.15799913029446</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BI32"/>
+  <autoFilter ref="A4:BI44"/>
   <mergeCells count="1">
     <mergeCell ref="A1:BI1"/>
   </mergeCells>
@@ -6942,7 +9426,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
